--- a/research/traditional_assets/database/data/pakistan/pakistan_machinery.xlsx
+++ b/research/traditional_assets/database/data/pakistan/pakistan_machinery.xlsx
@@ -1266,7 +1266,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1403,22 +1403,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.2145616394937645</v>
+        <v>0.2139713607392326</v>
       </c>
       <c r="C2">
-        <v>16.9</v>
+        <v>16.78716325104195</v>
       </c>
       <c r="D2">
-        <v>16.001</v>
+        <v>16.05716325104195</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>0.169</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.169</v>
       </c>
       <c r="G2">
         <v>0.899</v>
@@ -1439,28 +1439,28 @@
         <v>0.9379999999999999</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.008500699999999998</v>
       </c>
       <c r="N2">
-        <v>0.9379999999999999</v>
+        <v>0.9294992999999999</v>
       </c>
       <c r="O2">
-        <v>0.27202</v>
+        <v>0.269554797</v>
       </c>
       <c r="P2">
-        <v>0.66598</v>
+        <v>0.659944503</v>
       </c>
       <c r="Q2">
-        <v>1.26798</v>
+        <v>1.261944503</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.2145616394937645</v>
+        <v>0.2157719502416491</v>
       </c>
       <c r="T2">
-        <v>1.032125178898191</v>
+        <v>1.039527288767057</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1477,7 +1477,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>110.34385403555</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1485,22 +1485,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.2139713607392326</v>
+        <v>0.2133810819847007</v>
       </c>
       <c r="C3">
-        <v>16.78716325104195</v>
+        <v>16.67472215502377</v>
       </c>
       <c r="D3">
-        <v>16.05716325104195</v>
+        <v>16.11372215502377</v>
       </c>
       <c r="E3">
-        <v>0.169</v>
+        <v>0.338</v>
       </c>
       <c r="F3">
-        <v>0.169</v>
+        <v>0.338</v>
       </c>
       <c r="G3">
         <v>0.899</v>
@@ -1521,28 +1521,28 @@
         <v>0.9379999999999999</v>
       </c>
       <c r="M3">
-        <v>0.008500699999999998</v>
+        <v>0.0170014</v>
       </c>
       <c r="N3">
-        <v>0.9294992999999999</v>
+        <v>0.9209986</v>
       </c>
       <c r="O3">
-        <v>0.269554797</v>
+        <v>0.267089594</v>
       </c>
       <c r="P3">
-        <v>0.659944503</v>
+        <v>0.653909006</v>
       </c>
       <c r="Q3">
-        <v>1.261944503</v>
+        <v>1.255909006</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.2157719502416491</v>
+        <v>0.2170069612088782</v>
       </c>
       <c r="T3">
-        <v>1.039527288767057</v>
+        <v>1.047080462102634</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>110.34385403555</v>
+        <v>55.17192701777502</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1567,22 +1567,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.2133810819847007</v>
+        <v>0.2127908032301687</v>
       </c>
       <c r="C4">
-        <v>16.67472215502377</v>
+        <v>16.56268090760507</v>
       </c>
       <c r="D4">
-        <v>16.11372215502377</v>
+        <v>16.17068090760507</v>
       </c>
       <c r="E4">
-        <v>0.338</v>
+        <v>0.5069999999999999</v>
       </c>
       <c r="F4">
-        <v>0.338</v>
+        <v>0.5069999999999999</v>
       </c>
       <c r="G4">
         <v>0.899</v>
@@ -1603,28 +1603,28 @@
         <v>0.9379999999999999</v>
       </c>
       <c r="M4">
-        <v>0.0170014</v>
+        <v>0.02550209999999999</v>
       </c>
       <c r="N4">
-        <v>0.9209986</v>
+        <v>0.9124979</v>
       </c>
       <c r="O4">
-        <v>0.267089594</v>
+        <v>0.264624391</v>
       </c>
       <c r="P4">
-        <v>0.653909006</v>
+        <v>0.6478735090000001</v>
       </c>
       <c r="Q4">
-        <v>1.255909006</v>
+        <v>1.249873509</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.2170069612088782</v>
+        <v>0.2182674363197616</v>
       </c>
       <c r="T4">
-        <v>1.047080462102634</v>
+        <v>1.054789370970904</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>55.17192701777502</v>
+        <v>36.78128467851668</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1649,22 +1649,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.2127908032301687</v>
+        <v>0.2122005244756368</v>
       </c>
       <c r="C5">
-        <v>16.56268090760507</v>
+        <v>16.4510437639792</v>
       </c>
       <c r="D5">
-        <v>16.17068090760507</v>
+        <v>16.22804376397919</v>
       </c>
       <c r="E5">
-        <v>0.5069999999999999</v>
+        <v>0.6759999999999999</v>
       </c>
       <c r="F5">
-        <v>0.5069999999999999</v>
+        <v>0.6759999999999999</v>
       </c>
       <c r="G5">
         <v>0.899</v>
@@ -1685,28 +1685,28 @@
         <v>0.9379999999999999</v>
       </c>
       <c r="M5">
-        <v>0.02550209999999999</v>
+        <v>0.03400279999999999</v>
       </c>
       <c r="N5">
-        <v>0.9124979</v>
+        <v>0.9039971999999999</v>
       </c>
       <c r="O5">
-        <v>0.264624391</v>
+        <v>0.262159188</v>
       </c>
       <c r="P5">
-        <v>0.6478735090000001</v>
+        <v>0.641838012</v>
       </c>
       <c r="Q5">
-        <v>1.249873509</v>
+        <v>1.243838012</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.2182674363197616</v>
+        <v>0.2195541713287883</v>
       </c>
       <c r="T5">
-        <v>1.054789370970904</v>
+        <v>1.062658882107262</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>36.78128467851668</v>
+        <v>27.58596350888751</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1731,22 +1731,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.2122005244756368</v>
+        <v>0.2116102457211048</v>
       </c>
       <c r="C6">
-        <v>16.4510437639792</v>
+        <v>16.33981503993282</v>
       </c>
       <c r="D6">
-        <v>16.22804376397919</v>
+        <v>16.28581503993281</v>
       </c>
       <c r="E6">
-        <v>0.6759999999999999</v>
+        <v>0.845</v>
       </c>
       <c r="F6">
-        <v>0.6759999999999999</v>
+        <v>0.845</v>
       </c>
       <c r="G6">
         <v>0.899</v>
@@ -1767,28 +1767,28 @@
         <v>0.9379999999999999</v>
       </c>
       <c r="M6">
-        <v>0.03400279999999999</v>
+        <v>0.0425035</v>
       </c>
       <c r="N6">
-        <v>0.9039971999999999</v>
+        <v>0.8954964999999999</v>
       </c>
       <c r="O6">
-        <v>0.262159188</v>
+        <v>0.259693985</v>
       </c>
       <c r="P6">
-        <v>0.641838012</v>
+        <v>0.635802515</v>
       </c>
       <c r="Q6">
-        <v>1.243838012</v>
+        <v>1.237802515</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.2195541713287883</v>
+        <v>0.2208679954958999</v>
       </c>
       <c r="T6">
-        <v>1.062658882107262</v>
+        <v>1.070694067162281</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>27.58596350888751</v>
+        <v>22.06877080711</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1813,22 +1813,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.2116102457211048</v>
+        <v>0.211019966966573</v>
       </c>
       <c r="C7">
-        <v>16.33981503993282</v>
+        <v>16.22899911292838</v>
       </c>
       <c r="D7">
-        <v>16.28581503993281</v>
+        <v>16.34399911292838</v>
       </c>
       <c r="E7">
-        <v>0.845</v>
+        <v>1.014</v>
       </c>
       <c r="F7">
-        <v>0.845</v>
+        <v>1.014</v>
       </c>
       <c r="G7">
         <v>0.899</v>
@@ -1849,28 +1849,28 @@
         <v>0.9379999999999999</v>
       </c>
       <c r="M7">
-        <v>0.0425035</v>
+        <v>0.0510042</v>
       </c>
       <c r="N7">
-        <v>0.8954964999999999</v>
+        <v>0.8869958</v>
       </c>
       <c r="O7">
-        <v>0.259693985</v>
+        <v>0.257228782</v>
       </c>
       <c r="P7">
-        <v>0.635802515</v>
+        <v>0.629767018</v>
       </c>
       <c r="Q7">
-        <v>1.237802515</v>
+        <v>1.231767018</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.2208679954958999</v>
+        <v>0.2222097733686947</v>
       </c>
       <c r="T7">
-        <v>1.070694067162281</v>
+        <v>1.07890021360145</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1887,7 +1887,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>22.06877080711</v>
+        <v>18.39064233925833</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1895,22 +1895,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.211019966966573</v>
+        <v>0.2104296882120411</v>
       </c>
       <c r="C8">
-        <v>16.22899911292838</v>
+        <v>16.11860042320982</v>
       </c>
       <c r="D8">
-        <v>16.34399911292838</v>
+        <v>16.40260042320982</v>
       </c>
       <c r="E8">
-        <v>1.014</v>
+        <v>1.183</v>
       </c>
       <c r="F8">
-        <v>1.014</v>
+        <v>1.183</v>
       </c>
       <c r="G8">
         <v>0.899</v>
@@ -1931,28 +1931,28 @@
         <v>0.9379999999999999</v>
       </c>
       <c r="M8">
-        <v>0.05100419999999999</v>
+        <v>0.05950489999999999</v>
       </c>
       <c r="N8">
-        <v>0.8869958</v>
+        <v>0.8784951</v>
       </c>
       <c r="O8">
-        <v>0.257228782</v>
+        <v>0.254763579</v>
       </c>
       <c r="P8">
-        <v>0.629767018</v>
+        <v>0.6237315210000001</v>
       </c>
       <c r="Q8">
-        <v>1.231767018</v>
+        <v>1.225731521</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.2222097733686947</v>
+        <v>0.2235804066796141</v>
       </c>
       <c r="T8">
-        <v>1.07890021360145</v>
+        <v>1.087282836308127</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>18.39064233925834</v>
+        <v>15.76340771936429</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.2104296882120411</v>
+        <v>0.2098394094575091</v>
       </c>
       <c r="C9">
-        <v>16.11860042320982</v>
+        <v>16.00862347493207</v>
       </c>
       <c r="D9">
-        <v>16.40260042320982</v>
+        <v>16.46162347493206</v>
       </c>
       <c r="E9">
-        <v>1.183</v>
+        <v>1.352</v>
       </c>
       <c r="F9">
-        <v>1.183</v>
+        <v>1.352</v>
       </c>
       <c r="G9">
         <v>0.899</v>
@@ -2013,28 +2013,28 @@
         <v>0.9379999999999999</v>
       </c>
       <c r="M9">
-        <v>0.0595049</v>
+        <v>0.06800559999999999</v>
       </c>
       <c r="N9">
-        <v>0.8784951</v>
+        <v>0.8699943999999999</v>
       </c>
       <c r="O9">
-        <v>0.254763579</v>
+        <v>0.252298376</v>
       </c>
       <c r="P9">
-        <v>0.6237315210000001</v>
+        <v>0.617696024</v>
       </c>
       <c r="Q9">
-        <v>1.225731521</v>
+        <v>1.219696024</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.2235804066796141</v>
+        <v>0.2249808363668577</v>
       </c>
       <c r="T9">
-        <v>1.087282836308127</v>
+        <v>1.09584768994321</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>15.76340771936429</v>
+        <v>13.79298175444375</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2059,22 +2059,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.2098394094575091</v>
+        <v>0.2093449807029772</v>
       </c>
       <c r="C10">
-        <v>16.00862347493207</v>
+        <v>15.88939021162615</v>
       </c>
       <c r="D10">
-        <v>16.46162347493206</v>
+        <v>16.51139021162615</v>
       </c>
       <c r="E10">
-        <v>1.352</v>
+        <v>1.521</v>
       </c>
       <c r="F10">
-        <v>1.352</v>
+        <v>1.521</v>
       </c>
       <c r="G10">
         <v>0.899</v>
@@ -2095,45 +2095,45 @@
         <v>0.9379999999999999</v>
       </c>
       <c r="M10">
-        <v>0.06800559999999999</v>
+        <v>0.07878779999999999</v>
       </c>
       <c r="N10">
-        <v>0.8699943999999999</v>
+        <v>0.8592122</v>
       </c>
       <c r="O10">
-        <v>0.252298376</v>
+        <v>0.249171538</v>
       </c>
       <c r="P10">
-        <v>0.617696024</v>
+        <v>0.6100406620000001</v>
       </c>
       <c r="Q10">
-        <v>1.219696024</v>
+        <v>1.212040662</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.2249808363668577</v>
+        <v>0.2264120447285464</v>
       </c>
       <c r="T10">
-        <v>1.09584768994321</v>
+        <v>1.104600782119723</v>
       </c>
       <c r="U10">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V10">
         <v>0.29</v>
       </c>
       <c r="W10">
-        <v>0.03571299999999999</v>
+        <v>0.036778</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y10">
-        <v>13.79298175444375</v>
+        <v>11.90539652078114</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2141,22 +2141,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.2093449807029772</v>
+        <v>0.2087653519484453</v>
       </c>
       <c r="C11">
-        <v>15.88939021162615</v>
+        <v>15.77911727495298</v>
       </c>
       <c r="D11">
-        <v>16.51139021162615</v>
+        <v>16.57011727495297</v>
       </c>
       <c r="E11">
-        <v>1.521</v>
+        <v>1.69</v>
       </c>
       <c r="F11">
-        <v>1.521</v>
+        <v>1.69</v>
       </c>
       <c r="G11">
         <v>0.899</v>
@@ -2177,28 +2177,28 @@
         <v>0.9379999999999999</v>
       </c>
       <c r="M11">
-        <v>0.07878779999999999</v>
+        <v>0.08754199999999998</v>
       </c>
       <c r="N11">
-        <v>0.8592122</v>
+        <v>0.8504579999999999</v>
       </c>
       <c r="O11">
-        <v>0.249171538</v>
+        <v>0.24663282</v>
       </c>
       <c r="P11">
-        <v>0.6100406620000001</v>
+        <v>0.60382518</v>
       </c>
       <c r="Q11">
-        <v>1.212040662</v>
+        <v>1.20582518</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.2264120447285464</v>
+        <v>0.2278750577204948</v>
       </c>
       <c r="T11">
-        <v>1.104600782119723</v>
+        <v>1.113548387455715</v>
       </c>
       <c r="U11">
         <v>0.0518</v>
@@ -2215,7 +2215,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>11.90539652078114</v>
+        <v>10.71485686870302</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2223,22 +2223,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.2087653519484453</v>
+        <v>0.2083184931939134</v>
       </c>
       <c r="C12">
-        <v>15.77911727495298</v>
+        <v>15.6556782558753</v>
       </c>
       <c r="D12">
-        <v>16.57011727495297</v>
+        <v>16.6156782558753</v>
       </c>
       <c r="E12">
-        <v>1.69</v>
+        <v>1.859</v>
       </c>
       <c r="F12">
-        <v>1.69</v>
+        <v>1.859</v>
       </c>
       <c r="G12">
         <v>0.899</v>
@@ -2259,45 +2259,45 @@
         <v>0.9379999999999999</v>
       </c>
       <c r="M12">
-        <v>0.08754199999999999</v>
+        <v>0.09945649999999999</v>
       </c>
       <c r="N12">
-        <v>0.8504579999999999</v>
+        <v>0.8385435</v>
       </c>
       <c r="O12">
-        <v>0.24663282</v>
+        <v>0.243177615</v>
       </c>
       <c r="P12">
-        <v>0.60382518</v>
+        <v>0.595365885</v>
       </c>
       <c r="Q12">
-        <v>1.20582518</v>
+        <v>1.197365885</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.2278750577204948</v>
+        <v>0.2293709474088915</v>
       </c>
       <c r="T12">
-        <v>1.113548387455715</v>
+        <v>1.122697062574538</v>
       </c>
       <c r="U12">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V12">
         <v>0.29</v>
       </c>
       <c r="W12">
-        <v>0.036778</v>
+        <v>0.037985</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y12">
-        <v>10.71485686870302</v>
+        <v>9.431258892078446</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2305,22 +2305,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.2083184931939134</v>
+        <v>0.2077509344393814</v>
       </c>
       <c r="C13">
-        <v>15.6556782558753</v>
+        <v>15.54490807522925</v>
       </c>
       <c r="D13">
-        <v>16.6156782558753</v>
+        <v>16.67390807522925</v>
       </c>
       <c r="E13">
-        <v>1.859</v>
+        <v>2.028</v>
       </c>
       <c r="F13">
-        <v>1.859</v>
+        <v>2.028</v>
       </c>
       <c r="G13">
         <v>0.899</v>
@@ -2341,28 +2341,28 @@
         <v>0.9379999999999999</v>
       </c>
       <c r="M13">
-        <v>0.09945649999999999</v>
+        <v>0.108498</v>
       </c>
       <c r="N13">
-        <v>0.8385435</v>
+        <v>0.829502</v>
       </c>
       <c r="O13">
-        <v>0.243177615</v>
+        <v>0.24055558</v>
       </c>
       <c r="P13">
-        <v>0.595365885</v>
+        <v>0.58894642</v>
       </c>
       <c r="Q13">
-        <v>1.197365885</v>
+        <v>1.19094642</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.2293709474088915</v>
+        <v>0.2309008345902062</v>
       </c>
       <c r="T13">
-        <v>1.122697062574538</v>
+        <v>1.132053662127879</v>
       </c>
       <c r="U13">
         <v>0.0535</v>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>9.431258892078446</v>
+        <v>8.645320651071911</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2387,22 +2387,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.2077509344393814</v>
+        <v>0.2071833756848496</v>
       </c>
       <c r="C14">
-        <v>15.54490807522925</v>
+        <v>15.43454746395313</v>
       </c>
       <c r="D14">
-        <v>16.67390807522925</v>
+        <v>16.73254746395313</v>
       </c>
       <c r="E14">
-        <v>2.028</v>
+        <v>2.197</v>
       </c>
       <c r="F14">
-        <v>2.028</v>
+        <v>2.197</v>
       </c>
       <c r="G14">
         <v>0.899</v>
@@ -2423,28 +2423,28 @@
         <v>0.9379999999999999</v>
       </c>
       <c r="M14">
-        <v>0.108498</v>
+        <v>0.1175395</v>
       </c>
       <c r="N14">
-        <v>0.829502</v>
+        <v>0.8204604999999999</v>
       </c>
       <c r="O14">
-        <v>0.24055558</v>
+        <v>0.237933545</v>
       </c>
       <c r="P14">
-        <v>0.58894642</v>
+        <v>0.582526955</v>
       </c>
       <c r="Q14">
-        <v>1.19094642</v>
+        <v>1.184526955</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.2309008345902062</v>
+        <v>0.2324658915917811</v>
       </c>
       <c r="T14">
-        <v>1.132053662127879</v>
+        <v>1.141625355923827</v>
       </c>
       <c r="U14">
         <v>0.0535</v>
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>8.645320651071911</v>
+        <v>7.980295985604839</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2469,22 +2469,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.2071833756848496</v>
+        <v>0.2066953369303176</v>
       </c>
       <c r="C15">
-        <v>15.43454746395313</v>
+        <v>15.31630177281164</v>
       </c>
       <c r="D15">
-        <v>16.73254746395313</v>
+        <v>16.78330177281164</v>
       </c>
       <c r="E15">
-        <v>2.197</v>
+        <v>2.366</v>
       </c>
       <c r="F15">
-        <v>2.197</v>
+        <v>2.366</v>
       </c>
       <c r="G15">
         <v>0.899</v>
@@ -2505,45 +2505,45 @@
         <v>0.9379999999999999</v>
       </c>
       <c r="M15">
-        <v>0.1175395</v>
+        <v>0.1284738</v>
       </c>
       <c r="N15">
-        <v>0.8204604999999999</v>
+        <v>0.8095262</v>
       </c>
       <c r="O15">
-        <v>0.237933545</v>
+        <v>0.234762598</v>
       </c>
       <c r="P15">
-        <v>0.582526955</v>
+        <v>0.574763602</v>
       </c>
       <c r="Q15">
-        <v>1.184526955</v>
+        <v>1.176763602</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.2324658915917811</v>
+        <v>0.2340673452678112</v>
       </c>
       <c r="T15">
-        <v>1.141625355923827</v>
+        <v>1.151419647249912</v>
       </c>
       <c r="U15">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V15">
         <v>0.29</v>
       </c>
       <c r="W15">
-        <v>0.037985</v>
+        <v>0.038553</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y15">
-        <v>7.980295985604839</v>
+        <v>7.301099523793956</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2551,22 +2551,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.2066953369303176</v>
+        <v>0.2061334581757857</v>
       </c>
       <c r="C16">
-        <v>15.31630177281164</v>
+        <v>15.20611782283846</v>
       </c>
       <c r="D16">
-        <v>16.78330177281164</v>
+        <v>16.84211782283846</v>
       </c>
       <c r="E16">
-        <v>2.366</v>
+        <v>2.535</v>
       </c>
       <c r="F16">
-        <v>2.366</v>
+        <v>2.535</v>
       </c>
       <c r="G16">
         <v>0.899</v>
@@ -2587,28 +2587,28 @@
         <v>0.9379999999999999</v>
       </c>
       <c r="M16">
-        <v>0.1284738</v>
+        <v>0.1376505</v>
       </c>
       <c r="N16">
-        <v>0.8095262</v>
+        <v>0.8003494999999999</v>
       </c>
       <c r="O16">
-        <v>0.234762598</v>
+        <v>0.232101355</v>
       </c>
       <c r="P16">
-        <v>0.574763602</v>
+        <v>0.568248145</v>
       </c>
       <c r="Q16">
-        <v>1.176763602</v>
+        <v>1.170248145</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.2340673452678112</v>
+        <v>0.2357064802068067</v>
       </c>
       <c r="T16">
-        <v>1.151419647249912</v>
+        <v>1.161444392489553</v>
       </c>
       <c r="U16">
         <v>0.0543</v>
@@ -2625,7 +2625,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>7.301099523793956</v>
+        <v>6.814359555541025</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2633,22 +2633,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.2061334581757857</v>
+        <v>0.2055715794212538</v>
       </c>
       <c r="C17">
-        <v>15.20611782283846</v>
+        <v>15.09634755706438</v>
       </c>
       <c r="D17">
-        <v>16.84211782283846</v>
+        <v>16.90134755706438</v>
       </c>
       <c r="E17">
-        <v>2.535</v>
+        <v>2.704</v>
       </c>
       <c r="F17">
-        <v>2.535</v>
+        <v>2.704</v>
       </c>
       <c r="G17">
         <v>0.899</v>
@@ -2669,28 +2669,28 @@
         <v>0.9379999999999999</v>
       </c>
       <c r="M17">
-        <v>0.1376505</v>
+        <v>0.1468272</v>
       </c>
       <c r="N17">
-        <v>0.8003494999999999</v>
+        <v>0.7911728</v>
       </c>
       <c r="O17">
-        <v>0.232101355</v>
+        <v>0.229440112</v>
       </c>
       <c r="P17">
-        <v>0.568248145</v>
+        <v>0.561732688</v>
       </c>
       <c r="Q17">
-        <v>1.170248145</v>
+        <v>1.163732688</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.2357064802068067</v>
+        <v>0.2373846421681593</v>
       </c>
       <c r="T17">
-        <v>1.161444392489553</v>
+        <v>1.171707822139661</v>
       </c>
       <c r="U17">
         <v>0.0543</v>
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>6.814359555541026</v>
+        <v>6.388462083319713</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2715,22 +2715,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.2055715794212538</v>
+        <v>0.2051304006667219</v>
       </c>
       <c r="C18">
-        <v>15.09634755706438</v>
+        <v>14.97414663265783</v>
       </c>
       <c r="D18">
-        <v>16.90134755706438</v>
+        <v>16.94814663265783</v>
       </c>
       <c r="E18">
-        <v>2.704</v>
+        <v>2.873</v>
       </c>
       <c r="F18">
-        <v>2.704</v>
+        <v>2.873</v>
       </c>
       <c r="G18">
         <v>0.899</v>
@@ -2751,45 +2751,45 @@
         <v>0.9379999999999999</v>
       </c>
       <c r="M18">
-        <v>0.1468272</v>
+        <v>0.1588769</v>
       </c>
       <c r="N18">
-        <v>0.7911728</v>
+        <v>0.7791231</v>
       </c>
       <c r="O18">
-        <v>0.229440112</v>
+        <v>0.225945699</v>
       </c>
       <c r="P18">
-        <v>0.561732688</v>
+        <v>0.553177401</v>
       </c>
       <c r="Q18">
-        <v>1.163732688</v>
+        <v>1.155177401</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.2373846421681593</v>
+        <v>0.2391032417671348</v>
       </c>
       <c r="T18">
-        <v>1.171707822139661</v>
+        <v>1.182218563347603</v>
       </c>
       <c r="U18">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V18">
         <v>0.29</v>
       </c>
       <c r="W18">
-        <v>0.038553</v>
+        <v>0.039263</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y18">
-        <v>6.388462083319713</v>
+        <v>5.903941982755202</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2797,22 +2797,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.2051304006667219</v>
+        <v>0.20457562191219</v>
       </c>
       <c r="C19">
-        <v>14.97414663265783</v>
+        <v>14.86436524296622</v>
       </c>
       <c r="D19">
-        <v>16.94814663265783</v>
+        <v>17.00736524296622</v>
       </c>
       <c r="E19">
-        <v>2.873</v>
+        <v>3.042</v>
       </c>
       <c r="F19">
-        <v>2.873</v>
+        <v>3.042</v>
       </c>
       <c r="G19">
         <v>0.899</v>
@@ -2833,28 +2833,28 @@
         <v>0.9379999999999999</v>
       </c>
       <c r="M19">
-        <v>0.1588769</v>
+        <v>0.1682226</v>
       </c>
       <c r="N19">
-        <v>0.7791231</v>
+        <v>0.7697773999999999</v>
       </c>
       <c r="O19">
-        <v>0.225945699</v>
+        <v>0.223235446</v>
       </c>
       <c r="P19">
-        <v>0.553177401</v>
+        <v>0.5465419539999999</v>
       </c>
       <c r="Q19">
-        <v>1.155177401</v>
+        <v>1.148541954</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.2391032417671348</v>
+        <v>0.2408637584295</v>
       </c>
       <c r="T19">
-        <v>1.182218563347603</v>
+        <v>1.192985664097202</v>
       </c>
       <c r="U19">
         <v>0.0553</v>
@@ -2871,7 +2871,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>5.903941982755202</v>
+        <v>5.575945205935468</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2879,22 +2879,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.20457562191219</v>
+        <v>0.2040208431576581</v>
       </c>
       <c r="C20">
-        <v>14.86436524296621</v>
+        <v>14.75499913644737</v>
       </c>
       <c r="D20">
-        <v>17.00736524296621</v>
+        <v>17.06699913644737</v>
       </c>
       <c r="E20">
-        <v>3.042</v>
+        <v>3.211</v>
       </c>
       <c r="F20">
-        <v>3.042</v>
+        <v>3.211</v>
       </c>
       <c r="G20">
         <v>0.899</v>
@@ -2915,28 +2915,28 @@
         <v>0.9379999999999999</v>
       </c>
       <c r="M20">
-        <v>0.1682226</v>
+        <v>0.1775683</v>
       </c>
       <c r="N20">
-        <v>0.7697773999999999</v>
+        <v>0.7604316999999999</v>
       </c>
       <c r="O20">
-        <v>0.223235446</v>
+        <v>0.220525193</v>
       </c>
       <c r="P20">
-        <v>0.5465419539999999</v>
+        <v>0.539906507</v>
       </c>
       <c r="Q20">
-        <v>1.148541954</v>
+        <v>1.141906507</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.2408637584295</v>
+        <v>0.242667744639084</v>
       </c>
       <c r="T20">
-        <v>1.192985664097202</v>
+        <v>1.204018619186297</v>
       </c>
       <c r="U20">
         <v>0.0553</v>
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>5.575945205935469</v>
+        <v>5.282474405623076</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2961,22 +2961,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.2040208431576581</v>
+        <v>0.2034660644031261</v>
       </c>
       <c r="C21">
-        <v>14.75499913644737</v>
+        <v>14.64605269686546</v>
       </c>
       <c r="D21">
-        <v>17.06699913644737</v>
+        <v>17.12705269686546</v>
       </c>
       <c r="E21">
-        <v>3.211</v>
+        <v>3.38</v>
       </c>
       <c r="F21">
-        <v>3.211</v>
+        <v>3.38</v>
       </c>
       <c r="G21">
         <v>0.899</v>
@@ -2997,28 +2997,28 @@
         <v>0.9379999999999999</v>
       </c>
       <c r="M21">
-        <v>0.1775683</v>
+        <v>0.186914</v>
       </c>
       <c r="N21">
-        <v>0.7604316999999999</v>
+        <v>0.7510859999999999</v>
       </c>
       <c r="O21">
-        <v>0.220525193</v>
+        <v>0.21781494</v>
       </c>
       <c r="P21">
-        <v>0.539906507</v>
+        <v>0.5332710599999999</v>
       </c>
       <c r="Q21">
-        <v>1.141906507</v>
+        <v>1.13527106</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.242667744639084</v>
+        <v>0.2445168305039077</v>
       </c>
       <c r="T21">
-        <v>1.204018619186297</v>
+        <v>1.21532739815262</v>
       </c>
       <c r="U21">
         <v>0.0553</v>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>5.282474405623076</v>
+        <v>5.018350685341922</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.2034660644031261</v>
+        <v>0.2029112856485942</v>
       </c>
       <c r="C22">
-        <v>14.64605269686546</v>
+        <v>14.53753036990304</v>
       </c>
       <c r="D22">
-        <v>17.12705269686546</v>
+        <v>17.18753036990304</v>
       </c>
       <c r="E22">
-        <v>3.38</v>
+        <v>3.549</v>
       </c>
       <c r="F22">
-        <v>3.38</v>
+        <v>3.549</v>
       </c>
       <c r="G22">
         <v>0.899</v>
@@ -3079,28 +3079,28 @@
         <v>0.9379999999999999</v>
       </c>
       <c r="M22">
-        <v>0.186914</v>
+        <v>0.1962597</v>
       </c>
       <c r="N22">
-        <v>0.7510859999999999</v>
+        <v>0.7417402999999999</v>
       </c>
       <c r="O22">
-        <v>0.21781494</v>
+        <v>0.215104687</v>
       </c>
       <c r="P22">
-        <v>0.5332710599999999</v>
+        <v>0.5266356129999999</v>
       </c>
       <c r="Q22">
-        <v>1.13527106</v>
+        <v>1.128635613</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.2445168305039077</v>
+        <v>0.2464127286691066</v>
       </c>
       <c r="T22">
-        <v>1.21532739815262</v>
+        <v>1.226922475320622</v>
       </c>
       <c r="U22">
         <v>0.0553</v>
@@ -3117,7 +3117,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>5.018350685341922</v>
+        <v>4.779381605087544</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3125,22 +3125,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.2029112856485942</v>
+        <v>0.2023565068940623</v>
       </c>
       <c r="C23">
-        <v>14.53753036990304</v>
+        <v>14.42943666425813</v>
       </c>
       <c r="D23">
-        <v>17.18753036990304</v>
+        <v>17.24843666425813</v>
       </c>
       <c r="E23">
-        <v>3.548999999999999</v>
+        <v>3.718</v>
       </c>
       <c r="F23">
-        <v>3.548999999999999</v>
+        <v>3.718</v>
       </c>
       <c r="G23">
         <v>0.899</v>
@@ -3161,28 +3161,28 @@
         <v>0.9379999999999999</v>
       </c>
       <c r="M23">
-        <v>0.1962597</v>
+        <v>0.2056054</v>
       </c>
       <c r="N23">
-        <v>0.7417403</v>
+        <v>0.7323945999999999</v>
       </c>
       <c r="O23">
-        <v>0.215104687</v>
+        <v>0.212394434</v>
       </c>
       <c r="P23">
-        <v>0.5266356130000001</v>
+        <v>0.520000166</v>
       </c>
       <c r="Q23">
-        <v>1.128635613</v>
+        <v>1.122000166</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.2464127286691066</v>
+        <v>0.2483572396077722</v>
       </c>
       <c r="T23">
-        <v>1.226922475320622</v>
+        <v>1.238814862159598</v>
       </c>
       <c r="U23">
         <v>0.0553</v>
@@ -3199,7 +3199,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>4.779381605087545</v>
+        <v>4.562136986674474</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3207,22 +3207,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.2023565068940623</v>
+        <v>0.2022099781395304</v>
       </c>
       <c r="C24">
-        <v>14.42943666425813</v>
+        <v>14.27659542837344</v>
       </c>
       <c r="D24">
-        <v>17.24843666425813</v>
+        <v>17.26459542837344</v>
       </c>
       <c r="E24">
-        <v>3.718</v>
+        <v>3.887</v>
       </c>
       <c r="F24">
-        <v>3.718</v>
+        <v>3.887</v>
       </c>
       <c r="G24">
         <v>0.899</v>
@@ -3243,45 +3243,45 @@
         <v>0.9379999999999999</v>
       </c>
       <c r="M24">
-        <v>0.2056054</v>
+        <v>0.2246686</v>
       </c>
       <c r="N24">
-        <v>0.7323945999999999</v>
+        <v>0.7133313999999999</v>
       </c>
       <c r="O24">
-        <v>0.212394434</v>
+        <v>0.206866106</v>
       </c>
       <c r="P24">
-        <v>0.520000166</v>
+        <v>0.506465294</v>
       </c>
       <c r="Q24">
-        <v>1.122000166</v>
+        <v>1.108465294</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.2483572396077722</v>
+        <v>0.2503522573240654</v>
       </c>
       <c r="T24">
-        <v>1.238814862159598</v>
+        <v>1.251016142163223</v>
       </c>
       <c r="U24">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V24">
         <v>0.29</v>
       </c>
       <c r="W24">
-        <v>0.039263</v>
+        <v>0.041038</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y24">
-        <v>4.562136986674474</v>
+        <v>4.175038256347348</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3289,22 +3289,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.2022099781395304</v>
+        <v>0.2016729493849984</v>
       </c>
       <c r="C25">
-        <v>14.27659542837344</v>
+        <v>14.16707710378266</v>
       </c>
       <c r="D25">
-        <v>17.26459542837344</v>
+        <v>17.32407710378266</v>
       </c>
       <c r="E25">
-        <v>3.887</v>
+        <v>4.056</v>
       </c>
       <c r="F25">
-        <v>3.887</v>
+        <v>4.056</v>
       </c>
       <c r="G25">
         <v>0.899</v>
@@ -3325,28 +3325,28 @@
         <v>0.9379999999999999</v>
       </c>
       <c r="M25">
-        <v>0.2246686</v>
+        <v>0.2344368</v>
       </c>
       <c r="N25">
-        <v>0.7133313999999999</v>
+        <v>0.7035631999999999</v>
       </c>
       <c r="O25">
-        <v>0.206866106</v>
+        <v>0.204033328</v>
       </c>
       <c r="P25">
-        <v>0.506465294</v>
+        <v>0.499529872</v>
       </c>
       <c r="Q25">
-        <v>1.108465294</v>
+        <v>1.101529872</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.2503522573240654</v>
+        <v>0.2523997755065769</v>
       </c>
       <c r="T25">
-        <v>1.251016142163223</v>
+        <v>1.263538508482733</v>
       </c>
       <c r="U25">
         <v>0.0578</v>
@@ -3363,7 +3363,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>4.175038256347348</v>
+        <v>4.001078328999542</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3371,22 +3371,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.2016729493849984</v>
+        <v>0.2017571706304665</v>
       </c>
       <c r="C26">
-        <v>14.16707710378267</v>
+        <v>13.98872161634744</v>
       </c>
       <c r="D26">
-        <v>17.32407710378266</v>
+        <v>17.31472161634744</v>
       </c>
       <c r="E26">
-        <v>4.055999999999999</v>
+        <v>4.225</v>
       </c>
       <c r="F26">
-        <v>4.055999999999999</v>
+        <v>4.225</v>
       </c>
       <c r="G26">
         <v>0.899</v>
@@ -3407,45 +3407,45 @@
         <v>0.9379999999999999</v>
       </c>
       <c r="M26">
-        <v>0.2344368</v>
+        <v>0.2589925</v>
       </c>
       <c r="N26">
-        <v>0.7035631999999999</v>
+        <v>0.6790075</v>
       </c>
       <c r="O26">
-        <v>0.204033328</v>
+        <v>0.196912175</v>
       </c>
       <c r="P26">
-        <v>0.499529872</v>
+        <v>0.482095325</v>
       </c>
       <c r="Q26">
-        <v>1.101529872</v>
+        <v>1.084095325</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.2523997755065769</v>
+        <v>0.2545018941739554</v>
       </c>
       <c r="T26">
-        <v>1.263538508482733</v>
+        <v>1.276394804570763</v>
       </c>
       <c r="U26">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V26">
         <v>0.29</v>
       </c>
       <c r="W26">
-        <v>0.041038</v>
+        <v>0.043523</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y26">
-        <v>4.001078328999543</v>
+        <v>3.62172649787156</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3453,22 +3453,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.2017571706304665</v>
+        <v>0.2017618718759346</v>
       </c>
       <c r="C27">
-        <v>13.98872161634744</v>
+        <v>13.8191996890613</v>
       </c>
       <c r="D27">
-        <v>17.31472161634744</v>
+        <v>17.3141996890613</v>
       </c>
       <c r="E27">
-        <v>4.225</v>
+        <v>4.394</v>
       </c>
       <c r="F27">
-        <v>4.225</v>
+        <v>4.394</v>
       </c>
       <c r="G27">
         <v>0.899</v>
@@ -3489,45 +3489,45 @@
         <v>0.9379999999999999</v>
       </c>
       <c r="M27">
-        <v>0.2589925</v>
+        <v>0.2816554</v>
       </c>
       <c r="N27">
-        <v>0.6790075</v>
+        <v>0.6563445999999999</v>
       </c>
       <c r="O27">
-        <v>0.196912175</v>
+        <v>0.190339934</v>
       </c>
       <c r="P27">
-        <v>0.482095325</v>
+        <v>0.466004666</v>
       </c>
       <c r="Q27">
-        <v>1.084095325</v>
+        <v>1.068004666</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.2545018941739554</v>
+        <v>0.2566608268593711</v>
       </c>
       <c r="T27">
-        <v>1.276394804570763</v>
+        <v>1.289598568120632</v>
       </c>
       <c r="U27">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V27">
         <v>0.29</v>
       </c>
       <c r="W27">
-        <v>0.043523</v>
+        <v>0.045511</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y27">
-        <v>3.62172649787156</v>
+        <v>3.330310727221988</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3535,22 +3535,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.2017618718759346</v>
+        <v>0.2012695731214027</v>
       </c>
       <c r="C28">
-        <v>13.8191996890613</v>
+        <v>13.70502558696214</v>
       </c>
       <c r="D28">
-        <v>17.3141996890613</v>
+        <v>17.36902558696214</v>
       </c>
       <c r="E28">
-        <v>4.394</v>
+        <v>4.563</v>
       </c>
       <c r="F28">
-        <v>4.394</v>
+        <v>4.563</v>
       </c>
       <c r="G28">
         <v>0.899</v>
@@ -3571,28 +3571,28 @@
         <v>0.9379999999999999</v>
       </c>
       <c r="M28">
-        <v>0.2816554</v>
+        <v>0.2924883</v>
       </c>
       <c r="N28">
-        <v>0.6563445999999999</v>
+        <v>0.6455116999999999</v>
       </c>
       <c r="O28">
-        <v>0.190339934</v>
+        <v>0.187198393</v>
       </c>
       <c r="P28">
-        <v>0.466004666</v>
+        <v>0.4583133069999999</v>
       </c>
       <c r="Q28">
-        <v>1.068004666</v>
+        <v>1.060313307</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.2566608268593711</v>
+        <v>0.2588789083854832</v>
       </c>
       <c r="T28">
-        <v>1.289598568120632</v>
+        <v>1.303164078617072</v>
       </c>
       <c r="U28">
         <v>0.0641</v>
@@ -3609,7 +3609,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>3.330310727221988</v>
+        <v>3.206965885473025</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3617,22 +3617,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.2012695731214027</v>
+        <v>0.2007772743668708</v>
       </c>
       <c r="C29">
-        <v>13.70502558696214</v>
+        <v>13.59119980330339</v>
       </c>
       <c r="D29">
-        <v>17.36902558696214</v>
+        <v>17.42419980330338</v>
       </c>
       <c r="E29">
-        <v>4.563</v>
+        <v>4.732</v>
       </c>
       <c r="F29">
-        <v>4.563</v>
+        <v>4.732</v>
       </c>
       <c r="G29">
         <v>0.899</v>
@@ -3653,28 +3653,28 @@
         <v>0.9379999999999999</v>
       </c>
       <c r="M29">
-        <v>0.2924883</v>
+        <v>0.3033212</v>
       </c>
       <c r="N29">
-        <v>0.6455116999999999</v>
+        <v>0.6346787999999999</v>
       </c>
       <c r="O29">
-        <v>0.187198393</v>
+        <v>0.184056852</v>
       </c>
       <c r="P29">
-        <v>0.4583133069999999</v>
+        <v>0.4506219479999999</v>
       </c>
       <c r="Q29">
-        <v>1.060313307</v>
+        <v>1.052621948</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.2588789083854832</v>
+        <v>0.2611586032873205</v>
       </c>
       <c r="T29">
-        <v>1.303164078617072</v>
+        <v>1.317106408849525</v>
       </c>
       <c r="U29">
         <v>0.0641</v>
@@ -3691,7 +3691,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>3.206965885473025</v>
+        <v>3.092431389563274</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3699,22 +3699,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.2007772743668708</v>
+        <v>0.2018909956123389</v>
       </c>
       <c r="C30">
-        <v>13.59119980330339</v>
+        <v>13.29787679908337</v>
       </c>
       <c r="D30">
-        <v>17.42419980330338</v>
+        <v>17.29987679908337</v>
       </c>
       <c r="E30">
-        <v>4.732</v>
+        <v>4.901</v>
       </c>
       <c r="F30">
-        <v>4.732</v>
+        <v>4.901</v>
       </c>
       <c r="G30">
         <v>0.899</v>
@@ -3735,45 +3735,45 @@
         <v>0.9379999999999999</v>
       </c>
       <c r="M30">
-        <v>0.3033212</v>
+        <v>0.3523819</v>
       </c>
       <c r="N30">
-        <v>0.6346787999999999</v>
+        <v>0.5856180999999999</v>
       </c>
       <c r="O30">
-        <v>0.184056852</v>
+        <v>0.169829249</v>
       </c>
       <c r="P30">
-        <v>0.4506219479999999</v>
+        <v>0.415788851</v>
       </c>
       <c r="Q30">
-        <v>1.052621948</v>
+        <v>1.017788851</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.2611586032873205</v>
+        <v>0.2635025149469561</v>
       </c>
       <c r="T30">
-        <v>1.317106408849525</v>
+        <v>1.331441480778667</v>
       </c>
       <c r="U30">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V30">
         <v>0.29</v>
       </c>
       <c r="W30">
-        <v>0.045511</v>
+        <v>0.051049</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y30">
-        <v>3.092431389563274</v>
+        <v>2.661884733580243</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3781,22 +3781,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.2018909956123389</v>
+        <v>0.2014540768578069</v>
       </c>
       <c r="C31">
-        <v>13.29787679908337</v>
+        <v>13.17743730438588</v>
       </c>
       <c r="D31">
-        <v>17.29987679908337</v>
+        <v>17.34843730438588</v>
       </c>
       <c r="E31">
-        <v>4.900999999999999</v>
+        <v>5.069999999999999</v>
       </c>
       <c r="F31">
-        <v>4.900999999999999</v>
+        <v>5.069999999999999</v>
       </c>
       <c r="G31">
         <v>0.899</v>
@@ -3817,28 +3817,28 @@
         <v>0.9379999999999999</v>
       </c>
       <c r="M31">
-        <v>0.3523819</v>
+        <v>0.364533</v>
       </c>
       <c r="N31">
-        <v>0.5856181</v>
+        <v>0.5734669999999999</v>
       </c>
       <c r="O31">
-        <v>0.169829249</v>
+        <v>0.16630543</v>
       </c>
       <c r="P31">
-        <v>0.4157888510000001</v>
+        <v>0.40716157</v>
       </c>
       <c r="Q31">
-        <v>1.017788851</v>
+        <v>1.00916157</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.2635025149469561</v>
+        <v>0.2659133955111528</v>
       </c>
       <c r="T31">
-        <v>1.331441480778667</v>
+        <v>1.346186126191498</v>
       </c>
       <c r="U31">
         <v>0.07190000000000001</v>
@@ -3855,7 +3855,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>2.661884733580244</v>
+        <v>2.573155242460902</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3863,22 +3863,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.2014540768578069</v>
+        <v>0.201875548103275</v>
       </c>
       <c r="C32">
-        <v>13.17743730438588</v>
+        <v>12.96158904681791</v>
       </c>
       <c r="D32">
-        <v>17.34843730438588</v>
+        <v>17.30158904681791</v>
       </c>
       <c r="E32">
-        <v>5.069999999999999</v>
+        <v>5.239</v>
       </c>
       <c r="F32">
-        <v>5.069999999999999</v>
+        <v>5.239</v>
       </c>
       <c r="G32">
         <v>0.899</v>
@@ -3899,45 +3899,45 @@
         <v>0.9379999999999999</v>
       </c>
       <c r="M32">
-        <v>0.364533</v>
+        <v>0.3971162</v>
       </c>
       <c r="N32">
-        <v>0.5734669999999999</v>
+        <v>0.5408837999999999</v>
       </c>
       <c r="O32">
-        <v>0.16630543</v>
+        <v>0.156856302</v>
       </c>
       <c r="P32">
-        <v>0.40716157</v>
+        <v>0.3840274979999999</v>
       </c>
       <c r="Q32">
-        <v>1.00916157</v>
+        <v>0.986027498</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.2659133955111528</v>
+        <v>0.2683941566714131</v>
       </c>
       <c r="T32">
-        <v>1.346186126191498</v>
+        <v>1.361358152630788</v>
       </c>
       <c r="U32">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V32">
         <v>0.29</v>
       </c>
       <c r="W32">
-        <v>0.051049</v>
+        <v>0.053818</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y32">
-        <v>2.573155242460902</v>
+        <v>2.362029048424617</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3945,22 +3945,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.201875548103275</v>
+        <v>0.2014663193487432</v>
       </c>
       <c r="C33">
-        <v>12.96158904681791</v>
+        <v>12.83807292391267</v>
       </c>
       <c r="D33">
-        <v>17.30158904681791</v>
+        <v>17.34707292391267</v>
       </c>
       <c r="E33">
-        <v>5.239</v>
+        <v>5.407999999999999</v>
       </c>
       <c r="F33">
-        <v>5.239</v>
+        <v>5.407999999999999</v>
       </c>
       <c r="G33">
         <v>0.899</v>
@@ -3981,28 +3981,28 @@
         <v>0.9379999999999999</v>
       </c>
       <c r="M33">
-        <v>0.3971162</v>
+        <v>0.4099264</v>
       </c>
       <c r="N33">
-        <v>0.5408837999999999</v>
+        <v>0.5280735999999999</v>
       </c>
       <c r="O33">
-        <v>0.156856302</v>
+        <v>0.153141344</v>
       </c>
       <c r="P33">
-        <v>0.3840274979999999</v>
+        <v>0.374932256</v>
       </c>
       <c r="Q33">
-        <v>0.986027498</v>
+        <v>0.976932256</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.2683941566714131</v>
+        <v>0.2709478813952105</v>
       </c>
       <c r="T33">
-        <v>1.361358152630788</v>
+        <v>1.376976415141822</v>
       </c>
       <c r="U33">
         <v>0.07580000000000001</v>
@@ -4019,7 +4019,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>2.362029048424617</v>
+        <v>2.288215640661348</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4027,22 +4027,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.2014663193487432</v>
+        <v>0.2010570905942112</v>
       </c>
       <c r="C34">
-        <v>12.83807292391267</v>
+        <v>12.71479657505323</v>
       </c>
       <c r="D34">
-        <v>17.34707292391267</v>
+        <v>17.39279657505323</v>
       </c>
       <c r="E34">
-        <v>5.407999999999999</v>
+        <v>5.577</v>
       </c>
       <c r="F34">
-        <v>5.407999999999999</v>
+        <v>5.577</v>
       </c>
       <c r="G34">
         <v>0.899</v>
@@ -4063,28 +4063,28 @@
         <v>0.9379999999999999</v>
       </c>
       <c r="M34">
-        <v>0.4099264</v>
+        <v>0.4227366</v>
       </c>
       <c r="N34">
-        <v>0.5280735999999999</v>
+        <v>0.5152633999999999</v>
       </c>
       <c r="O34">
-        <v>0.153141344</v>
+        <v>0.149426386</v>
       </c>
       <c r="P34">
-        <v>0.374932256</v>
+        <v>0.365837014</v>
       </c>
       <c r="Q34">
-        <v>0.976932256</v>
+        <v>0.9678370140000001</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.2709478813952105</v>
+        <v>0.2735778367077779</v>
       </c>
       <c r="T34">
-        <v>1.376976415141822</v>
+        <v>1.39306089444423</v>
       </c>
       <c r="U34">
         <v>0.07580000000000001</v>
@@ -4101,7 +4101,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>2.288215640661348</v>
+        <v>2.218875772762519</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.2010570905942112</v>
+        <v>0.2006478618396793</v>
       </c>
       <c r="C35">
-        <v>12.71479657505323</v>
+        <v>12.59176190124937</v>
       </c>
       <c r="D35">
-        <v>17.39279657505323</v>
+        <v>17.43876190124937</v>
       </c>
       <c r="E35">
-        <v>5.577</v>
+        <v>5.746</v>
       </c>
       <c r="F35">
-        <v>5.577</v>
+        <v>5.746</v>
       </c>
       <c r="G35">
         <v>0.899</v>
@@ -4145,28 +4145,28 @@
         <v>0.9379999999999999</v>
       </c>
       <c r="M35">
-        <v>0.4227366</v>
+        <v>0.4355468</v>
       </c>
       <c r="N35">
-        <v>0.5152633999999999</v>
+        <v>0.5024531999999999</v>
       </c>
       <c r="O35">
-        <v>0.149426386</v>
+        <v>0.145711428</v>
       </c>
       <c r="P35">
-        <v>0.365837014</v>
+        <v>0.356741772</v>
       </c>
       <c r="Q35">
-        <v>0.9678370140000001</v>
+        <v>0.958741772</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.2735778367077779</v>
+        <v>0.2762874876358777</v>
       </c>
       <c r="T35">
-        <v>1.39306089444423</v>
+        <v>1.409632782210348</v>
       </c>
       <c r="U35">
         <v>0.07580000000000001</v>
@@ -4183,7 +4183,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>2.218875772762519</v>
+        <v>2.153614720622445</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4191,22 +4191,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.2006478618396793</v>
+        <v>0.2002386330851474</v>
       </c>
       <c r="C36">
-        <v>12.59176190124937</v>
+        <v>12.46897082365994</v>
       </c>
       <c r="D36">
-        <v>17.43876190124937</v>
+        <v>17.48497082365994</v>
       </c>
       <c r="E36">
-        <v>5.746</v>
+        <v>5.915</v>
       </c>
       <c r="F36">
-        <v>5.746</v>
+        <v>5.915</v>
       </c>
       <c r="G36">
         <v>0.899</v>
@@ -4227,28 +4227,28 @@
         <v>0.9379999999999999</v>
       </c>
       <c r="M36">
-        <v>0.4355468</v>
+        <v>0.4483570000000001</v>
       </c>
       <c r="N36">
-        <v>0.5024531999999999</v>
+        <v>0.4896429999999999</v>
       </c>
       <c r="O36">
-        <v>0.145711428</v>
+        <v>0.14199647</v>
       </c>
       <c r="P36">
-        <v>0.356741772</v>
+        <v>0.3476465299999999</v>
       </c>
       <c r="Q36">
-        <v>0.958741772</v>
+        <v>0.94964653</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.2762874876358777</v>
+        <v>0.2790805124386883</v>
       </c>
       <c r="T36">
-        <v>1.409632782210348</v>
+        <v>1.426714574215423</v>
       </c>
       <c r="U36">
         <v>0.07580000000000001</v>
@@ -4265,7 +4265,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>2.153614720622445</v>
+        <v>2.092082871461804</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4273,22 +4273,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.2002386330851474</v>
+        <v>0.1998294043306154</v>
       </c>
       <c r="C37">
-        <v>12.46897082365994</v>
+        <v>12.34642528386051</v>
       </c>
       <c r="D37">
-        <v>17.48497082365994</v>
+        <v>17.53142528386051</v>
       </c>
       <c r="E37">
-        <v>5.915</v>
+        <v>6.084000000000001</v>
       </c>
       <c r="F37">
-        <v>5.915</v>
+        <v>6.084000000000001</v>
       </c>
       <c r="G37">
         <v>0.899</v>
@@ -4309,28 +4309,28 @@
         <v>0.9379999999999999</v>
       </c>
       <c r="M37">
-        <v>0.4483570000000001</v>
+        <v>0.4611672000000001</v>
       </c>
       <c r="N37">
-        <v>0.4896429999999999</v>
+        <v>0.4768327999999999</v>
       </c>
       <c r="O37">
-        <v>0.14199647</v>
+        <v>0.138281512</v>
       </c>
       <c r="P37">
-        <v>0.3476465299999999</v>
+        <v>0.3385512879999999</v>
       </c>
       <c r="Q37">
-        <v>0.94964653</v>
+        <v>0.940551288</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.2790805124386883</v>
+        <v>0.2819608192665867</v>
       </c>
       <c r="T37">
-        <v>1.426714574215423</v>
+        <v>1.444330172220656</v>
       </c>
       <c r="U37">
         <v>0.07580000000000001</v>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>2.092082871461804</v>
+        <v>2.033969458365642</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4355,22 +4355,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1998294043306155</v>
+        <v>0.2031505155760835</v>
       </c>
       <c r="C38">
-        <v>12.3464252838605</v>
+        <v>11.80739908187352</v>
       </c>
       <c r="D38">
-        <v>17.5314252838605</v>
+        <v>17.16139908187352</v>
       </c>
       <c r="E38">
-        <v>6.084</v>
+        <v>6.252999999999999</v>
       </c>
       <c r="F38">
-        <v>6.084</v>
+        <v>6.252999999999999</v>
       </c>
       <c r="G38">
         <v>0.899</v>
@@ -4391,45 +4391,45 @@
         <v>0.9379999999999999</v>
       </c>
       <c r="M38">
-        <v>0.4611672</v>
+        <v>0.5627699999999999</v>
       </c>
       <c r="N38">
-        <v>0.4768327999999999</v>
+        <v>0.3752300000000001</v>
       </c>
       <c r="O38">
-        <v>0.138281512</v>
+        <v>0.1088167</v>
       </c>
       <c r="P38">
-        <v>0.338551288</v>
+        <v>0.2664133000000001</v>
       </c>
       <c r="Q38">
-        <v>0.9405512880000001</v>
+        <v>0.8684133000000002</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.2819608192665867</v>
+        <v>0.2849325644064818</v>
       </c>
       <c r="T38">
-        <v>1.444330172220656</v>
+        <v>1.462504995559389</v>
       </c>
       <c r="U38">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V38">
         <v>0.29</v>
       </c>
       <c r="W38">
-        <v>0.053818</v>
+        <v>0.0639</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y38">
-        <v>2.033969458365642</v>
+        <v>1.666755512909359</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4437,22 +4437,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.2031505155760835</v>
+        <v>0.2028421068215516</v>
       </c>
       <c r="C39">
-        <v>11.80739908187352</v>
+        <v>11.67210167173294</v>
       </c>
       <c r="D39">
-        <v>17.16139908187352</v>
+        <v>17.19510167173294</v>
       </c>
       <c r="E39">
-        <v>6.252999999999999</v>
+        <v>6.422</v>
       </c>
       <c r="F39">
-        <v>6.252999999999999</v>
+        <v>6.422</v>
       </c>
       <c r="G39">
         <v>0.899</v>
@@ -4473,28 +4473,28 @@
         <v>0.9379999999999999</v>
       </c>
       <c r="M39">
-        <v>0.5627699999999999</v>
+        <v>0.5779799999999999</v>
       </c>
       <c r="N39">
-        <v>0.3752300000000001</v>
+        <v>0.36002</v>
       </c>
       <c r="O39">
-        <v>0.1088167</v>
+        <v>0.1044058</v>
       </c>
       <c r="P39">
-        <v>0.2664133000000001</v>
+        <v>0.2556142</v>
       </c>
       <c r="Q39">
-        <v>0.8684133000000002</v>
+        <v>0.8576142000000001</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.2849325644064818</v>
+        <v>0.2880001722928252</v>
       </c>
       <c r="T39">
-        <v>1.462504995559389</v>
+        <v>1.481266103521952</v>
       </c>
       <c r="U39">
         <v>0.09</v>
@@ -4511,7 +4511,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>1.666755512909359</v>
+        <v>1.622893525727534</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4519,22 +4519,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.2028421068215516</v>
+        <v>0.2025336980670197</v>
       </c>
       <c r="C40">
-        <v>11.67210167173294</v>
+        <v>11.53693689642317</v>
       </c>
       <c r="D40">
-        <v>17.19510167173294</v>
+        <v>17.22893689642317</v>
       </c>
       <c r="E40">
-        <v>6.422</v>
+        <v>6.590999999999999</v>
       </c>
       <c r="F40">
-        <v>6.422</v>
+        <v>6.590999999999999</v>
       </c>
       <c r="G40">
         <v>0.899</v>
@@ -4555,28 +4555,28 @@
         <v>0.9379999999999999</v>
       </c>
       <c r="M40">
-        <v>0.5779799999999999</v>
+        <v>0.5931899999999999</v>
       </c>
       <c r="N40">
-        <v>0.36002</v>
+        <v>0.3448100000000001</v>
       </c>
       <c r="O40">
-        <v>0.1044058</v>
+        <v>0.09999490000000001</v>
       </c>
       <c r="P40">
-        <v>0.2556142</v>
+        <v>0.2448151000000001</v>
       </c>
       <c r="Q40">
-        <v>0.8576142000000001</v>
+        <v>0.8468151000000002</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.2880001722928252</v>
+        <v>0.2911683574869176</v>
       </c>
       <c r="T40">
-        <v>1.481266103521952</v>
+        <v>1.50064232977837</v>
       </c>
       <c r="U40">
         <v>0.09</v>
@@ -4593,7 +4593,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>1.622893525727534</v>
+        <v>1.5812808712217</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4601,22 +4601,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.2025336980670197</v>
+        <v>0.2022252893124878</v>
       </c>
       <c r="C41">
-        <v>11.53693689642317</v>
+        <v>11.40190554045438</v>
       </c>
       <c r="D41">
-        <v>17.22893689642317</v>
+        <v>17.26290554045438</v>
       </c>
       <c r="E41">
-        <v>6.590999999999999</v>
+        <v>6.76</v>
       </c>
       <c r="F41">
-        <v>6.590999999999999</v>
+        <v>6.76</v>
       </c>
       <c r="G41">
         <v>0.899</v>
@@ -4637,28 +4637,28 @@
         <v>0.9379999999999999</v>
       </c>
       <c r="M41">
-        <v>0.5931899999999999</v>
+        <v>0.6083999999999999</v>
       </c>
       <c r="N41">
-        <v>0.3448100000000001</v>
+        <v>0.3296</v>
       </c>
       <c r="O41">
-        <v>0.09999490000000001</v>
+        <v>0.09558399999999999</v>
       </c>
       <c r="P41">
-        <v>0.2448151000000001</v>
+        <v>0.234016</v>
       </c>
       <c r="Q41">
-        <v>0.8468151000000002</v>
+        <v>0.8360160000000001</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.2911683574869176</v>
+        <v>0.2944421488541463</v>
       </c>
       <c r="T41">
-        <v>1.50064232977837</v>
+        <v>1.520664430243335</v>
       </c>
       <c r="U41">
         <v>0.09</v>
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>1.5812808712217</v>
+        <v>1.541748849441157</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4683,22 +4683,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.2022252893124878</v>
+        <v>0.2019168805579558</v>
       </c>
       <c r="C42">
-        <v>11.40190554045438</v>
+        <v>11.26700839453593</v>
       </c>
       <c r="D42">
-        <v>17.26290554045438</v>
+        <v>17.29700839453593</v>
       </c>
       <c r="E42">
-        <v>6.76</v>
+        <v>6.929</v>
       </c>
       <c r="F42">
-        <v>6.76</v>
+        <v>6.929</v>
       </c>
       <c r="G42">
         <v>0.899</v>
@@ -4719,28 +4719,28 @@
         <v>0.9379999999999999</v>
       </c>
       <c r="M42">
-        <v>0.6083999999999999</v>
+        <v>0.62361</v>
       </c>
       <c r="N42">
-        <v>0.3296</v>
+        <v>0.3143899999999999</v>
       </c>
       <c r="O42">
-        <v>0.09558399999999999</v>
+        <v>0.09117309999999998</v>
       </c>
       <c r="P42">
-        <v>0.234016</v>
+        <v>0.2232169</v>
       </c>
       <c r="Q42">
-        <v>0.8360160000000001</v>
+        <v>0.8252169</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.2944421488541463</v>
+        <v>0.2978269161999252</v>
       </c>
       <c r="T42">
-        <v>1.520664430243335</v>
+        <v>1.541365245978298</v>
       </c>
       <c r="U42">
         <v>0.09</v>
@@ -4757,7 +4757,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>1.541748849441157</v>
+        <v>1.504145218966983</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4765,22 +4765,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.2019168805579558</v>
+        <v>0.2223819437457783</v>
       </c>
       <c r="C43">
-        <v>11.26700839453593</v>
+        <v>9.09336192703471</v>
       </c>
       <c r="D43">
-        <v>17.29700839453593</v>
+        <v>15.29236192703471</v>
       </c>
       <c r="E43">
-        <v>6.929</v>
+        <v>7.098</v>
       </c>
       <c r="F43">
-        <v>6.929</v>
+        <v>7.098</v>
       </c>
       <c r="G43">
         <v>0.899</v>
@@ -4801,45 +4801,45 @@
         <v>0.9379999999999999</v>
       </c>
       <c r="M43">
-        <v>0.62361</v>
+        <v>1.0419864</v>
       </c>
       <c r="N43">
-        <v>0.3143899999999999</v>
+        <v>-0.1039864000000001</v>
       </c>
       <c r="O43">
-        <v>0.09117309999999998</v>
+        <v>-0.03015605600000004</v>
       </c>
       <c r="P43">
-        <v>0.2232169</v>
+        <v>-0.0738303440000001</v>
       </c>
       <c r="Q43">
-        <v>0.8252169</v>
+        <v>0.528169656</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.2978269161999252</v>
+        <v>0.3048651754033517</v>
       </c>
       <c r="T43">
-        <v>1.541365245978298</v>
+        <v>1.584410363110719</v>
       </c>
       <c r="U43">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V43">
-        <v>0.29</v>
+        <v>0.2610590694849759</v>
       </c>
       <c r="W43">
-        <v>0.0639</v>
+        <v>0.1084765285996055</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y43">
-        <v>1.504145218966983</v>
+        <v>0.9002036878792274</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4847,22 +4847,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.2223819437457784</v>
+        <v>0.2233919437457783</v>
       </c>
       <c r="C44">
-        <v>9.093361927034707</v>
+        <v>8.837391283994645</v>
       </c>
       <c r="D44">
-        <v>15.2923619270347</v>
+        <v>15.20539128399464</v>
       </c>
       <c r="E44">
-        <v>7.097999999999999</v>
+        <v>7.266999999999999</v>
       </c>
       <c r="F44">
-        <v>7.097999999999999</v>
+        <v>7.266999999999999</v>
       </c>
       <c r="G44">
         <v>0.899</v>
@@ -4883,37 +4883,37 @@
         <v>0.9379999999999999</v>
       </c>
       <c r="M44">
-        <v>1.0419864</v>
+        <v>1.0667956</v>
       </c>
       <c r="N44">
-        <v>-0.1039863999999999</v>
+        <v>-0.1287956000000001</v>
       </c>
       <c r="O44">
-        <v>-0.03015605599999998</v>
+        <v>-0.03735072400000003</v>
       </c>
       <c r="P44">
-        <v>-0.07383034399999995</v>
+        <v>-0.09144487600000009</v>
       </c>
       <c r="Q44">
-        <v>0.5281696560000001</v>
+        <v>0.510555124</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.3048651754033517</v>
+        <v>0.3094101784806035</v>
       </c>
       <c r="T44">
-        <v>1.584410363110719</v>
+        <v>1.612207036147749</v>
       </c>
       <c r="U44">
         <v>0.1468</v>
       </c>
       <c r="V44">
-        <v>0.261059069484976</v>
+        <v>0.2549879283341626</v>
       </c>
       <c r="W44">
-        <v>0.1084765285996055</v>
+        <v>0.109367772120545</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.9002036878792277</v>
+        <v>0.8792687183936641</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4929,22 +4929,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.2233919437457783</v>
+        <v>0.2244019437457783</v>
       </c>
       <c r="C45">
-        <v>8.837391283994645</v>
+        <v>8.582404284778697</v>
       </c>
       <c r="D45">
-        <v>15.20539128399464</v>
+        <v>15.1194042847787</v>
       </c>
       <c r="E45">
-        <v>7.266999999999999</v>
+        <v>7.435999999999999</v>
       </c>
       <c r="F45">
-        <v>7.266999999999999</v>
+        <v>7.435999999999999</v>
       </c>
       <c r="G45">
         <v>0.899</v>
@@ -4965,37 +4965,37 @@
         <v>0.9379999999999999</v>
       </c>
       <c r="M45">
-        <v>1.0667956</v>
+        <v>1.0916048</v>
       </c>
       <c r="N45">
-        <v>-0.1287956000000001</v>
+        <v>-0.1536048000000001</v>
       </c>
       <c r="O45">
-        <v>-0.03735072400000003</v>
+        <v>-0.04454539200000002</v>
       </c>
       <c r="P45">
-        <v>-0.09144487600000009</v>
+        <v>-0.1090594080000001</v>
       </c>
       <c r="Q45">
-        <v>0.510555124</v>
+        <v>0.492940592</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.3094101784806035</v>
+        <v>0.3141175030963286</v>
       </c>
       <c r="T45">
-        <v>1.612207036147749</v>
+        <v>1.640996447507531</v>
       </c>
       <c r="U45">
         <v>0.1468</v>
       </c>
       <c r="V45">
-        <v>0.2549879283341626</v>
+        <v>0.2491927481447498</v>
       </c>
       <c r="W45">
-        <v>0.109367772120545</v>
+        <v>0.1102185045723507</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5003,7 +5003,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.8792687183936641</v>
+        <v>0.8592853384301717</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5011,22 +5011,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.2244019437457783</v>
+        <v>0.2254119437457783</v>
       </c>
       <c r="C46">
-        <v>8.582404284778697</v>
+        <v>8.328384335608501</v>
       </c>
       <c r="D46">
-        <v>15.1194042847787</v>
+        <v>15.0343843356085</v>
       </c>
       <c r="E46">
-        <v>7.435999999999999</v>
+        <v>7.605</v>
       </c>
       <c r="F46">
-        <v>7.435999999999999</v>
+        <v>7.605</v>
       </c>
       <c r="G46">
         <v>0.899</v>
@@ -5047,37 +5047,37 @@
         <v>0.9379999999999999</v>
       </c>
       <c r="M46">
-        <v>1.0916048</v>
+        <v>1.116414</v>
       </c>
       <c r="N46">
-        <v>-0.1536048000000001</v>
+        <v>-0.1784140000000001</v>
       </c>
       <c r="O46">
-        <v>-0.04454539200000002</v>
+        <v>-0.05174006000000002</v>
       </c>
       <c r="P46">
-        <v>-0.1090594080000001</v>
+        <v>-0.12667394</v>
       </c>
       <c r="Q46">
-        <v>0.492940592</v>
+        <v>0.4753260600000001</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.3141175030963286</v>
+        <v>0.3189960031526254</v>
       </c>
       <c r="T46">
-        <v>1.640996447507531</v>
+        <v>1.670832746553122</v>
       </c>
       <c r="U46">
         <v>0.1468</v>
       </c>
       <c r="V46">
-        <v>0.2491927481447498</v>
+        <v>0.2436551315193109</v>
       </c>
       <c r="W46">
-        <v>0.1102185045723507</v>
+        <v>0.1110314266929652</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5085,7 +5085,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.8592853384301717</v>
+        <v>0.8401901086872791</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5093,22 +5093,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.2254119437457783</v>
+        <v>0.2264219437457783</v>
       </c>
       <c r="C47">
-        <v>8.328384335608501</v>
+        <v>8.075315213861384</v>
       </c>
       <c r="D47">
-        <v>15.0343843356085</v>
+        <v>14.95031521386139</v>
       </c>
       <c r="E47">
-        <v>7.605</v>
+        <v>7.774</v>
       </c>
       <c r="F47">
-        <v>7.605</v>
+        <v>7.774</v>
       </c>
       <c r="G47">
         <v>0.899</v>
@@ -5129,37 +5129,37 @@
         <v>0.9379999999999999</v>
       </c>
       <c r="M47">
-        <v>1.116414</v>
+        <v>1.1412232</v>
       </c>
       <c r="N47">
-        <v>-0.1784140000000001</v>
+        <v>-0.2032232000000003</v>
       </c>
       <c r="O47">
-        <v>-0.05174006000000002</v>
+        <v>-0.05893472800000008</v>
       </c>
       <c r="P47">
-        <v>-0.12667394</v>
+        <v>-0.1442884720000002</v>
       </c>
       <c r="Q47">
-        <v>0.4753260600000001</v>
+        <v>0.4577115279999999</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.3189960031526254</v>
+        <v>0.3240551883961926</v>
       </c>
       <c r="T47">
-        <v>1.670832746553122</v>
+        <v>1.701774093711513</v>
       </c>
       <c r="U47">
         <v>0.1468</v>
       </c>
       <c r="V47">
-        <v>0.2436551315193109</v>
+        <v>0.2383582808341085</v>
       </c>
       <c r="W47">
-        <v>0.1110314266929652</v>
+        <v>0.1118090043735529</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5167,7 +5167,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.8401901086872791</v>
+        <v>0.821925106324512</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.2264219437457783</v>
+        <v>0.2274319437457783</v>
       </c>
       <c r="C48">
-        <v>8.075315213861384</v>
+        <v>7.823181057750967</v>
       </c>
       <c r="D48">
-        <v>14.95031521386139</v>
+        <v>14.86718105775097</v>
       </c>
       <c r="E48">
-        <v>7.774</v>
+        <v>7.943</v>
       </c>
       <c r="F48">
-        <v>7.774</v>
+        <v>7.943</v>
       </c>
       <c r="G48">
         <v>0.899</v>
@@ -5211,37 +5211,37 @@
         <v>0.9379999999999999</v>
       </c>
       <c r="M48">
-        <v>1.1412232</v>
+        <v>1.1660324</v>
       </c>
       <c r="N48">
-        <v>-0.2032232000000003</v>
+        <v>-0.2280324</v>
       </c>
       <c r="O48">
-        <v>-0.05893472800000008</v>
+        <v>-0.06612939600000001</v>
       </c>
       <c r="P48">
-        <v>-0.1442884720000002</v>
+        <v>-0.161903004</v>
       </c>
       <c r="Q48">
-        <v>0.4577115279999999</v>
+        <v>0.4400969960000001</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.3240551883961926</v>
+        <v>0.3293052862904604</v>
       </c>
       <c r="T48">
-        <v>1.701774093711513</v>
+        <v>1.733883038875881</v>
       </c>
       <c r="U48">
         <v>0.1468</v>
       </c>
       <c r="V48">
-        <v>0.2383582808341085</v>
+        <v>0.2332868280504041</v>
       </c>
       <c r="W48">
-        <v>0.1118090043735529</v>
+        <v>0.1125534936422007</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5249,7 +5249,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.821925106324512</v>
+        <v>0.8044373381048416</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5257,22 +5257,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.2274319437457783</v>
+        <v>0.259338075414256</v>
       </c>
       <c r="C49">
-        <v>7.823181057750967</v>
+        <v>5.432777519073058</v>
       </c>
       <c r="D49">
-        <v>14.86718105775097</v>
+        <v>12.64577751907306</v>
       </c>
       <c r="E49">
-        <v>7.943</v>
+        <v>8.112</v>
       </c>
       <c r="F49">
-        <v>7.943</v>
+        <v>8.112</v>
       </c>
       <c r="G49">
         <v>0.899</v>
@@ -5293,45 +5293,45 @@
         <v>0.9379999999999999</v>
       </c>
       <c r="M49">
-        <v>1.1660324</v>
+        <v>1.6288896</v>
       </c>
       <c r="N49">
-        <v>-0.2280324</v>
+        <v>-0.6908896000000002</v>
       </c>
       <c r="O49">
-        <v>-0.06612939600000001</v>
+        <v>-0.200357984</v>
       </c>
       <c r="P49">
-        <v>-0.161903004</v>
+        <v>-0.4905316160000002</v>
       </c>
       <c r="Q49">
-        <v>0.4400969960000001</v>
+        <v>0.1114683839999999</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.3293052862904604</v>
+        <v>0.344326795004657</v>
       </c>
       <c r="T49">
-        <v>1.733883038875881</v>
+        <v>1.825752716223581</v>
       </c>
       <c r="U49">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V49">
-        <v>0.2332868280504041</v>
+        <v>0.1669971985823962</v>
       </c>
       <c r="W49">
-        <v>0.1125534936422007</v>
+        <v>0.1672669625246548</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y49">
-        <v>0.8044373381048416</v>
+        <v>0.5758524089048146</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5339,22 +5339,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.2593380754142559</v>
+        <v>0.260888075414256</v>
       </c>
       <c r="C50">
-        <v>5.432777519073063</v>
+        <v>5.172647617441775</v>
       </c>
       <c r="D50">
-        <v>12.64577751907306</v>
+        <v>12.55464761744177</v>
       </c>
       <c r="E50">
-        <v>8.111999999999998</v>
+        <v>8.280999999999999</v>
       </c>
       <c r="F50">
-        <v>8.111999999999998</v>
+        <v>8.280999999999999</v>
       </c>
       <c r="G50">
         <v>0.899</v>
@@ -5375,37 +5375,37 @@
         <v>0.9379999999999999</v>
       </c>
       <c r="M50">
-        <v>1.6288896</v>
+        <v>1.6628248</v>
       </c>
       <c r="N50">
-        <v>-0.6908895999999998</v>
+        <v>-0.7248247999999999</v>
       </c>
       <c r="O50">
-        <v>-0.2003579839999999</v>
+        <v>-0.210199192</v>
       </c>
       <c r="P50">
-        <v>-0.4905316159999998</v>
+        <v>-0.514625608</v>
       </c>
       <c r="Q50">
-        <v>0.1114683840000003</v>
+        <v>0.08737439200000008</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.344326795004657</v>
+        <v>0.3501802615733757</v>
       </c>
       <c r="T50">
-        <v>1.825752716223581</v>
+        <v>1.861551789090709</v>
       </c>
       <c r="U50">
         <v>0.2008</v>
       </c>
       <c r="V50">
-        <v>0.1669971985823963</v>
+        <v>0.163589092488878</v>
       </c>
       <c r="W50">
-        <v>0.1672669625246548</v>
+        <v>0.1679513102282333</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.5758524089048147</v>
+        <v>0.5641003189271654</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5421,22 +5421,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.260888075414256</v>
+        <v>0.262438075414256</v>
       </c>
       <c r="C51">
-        <v>5.172647617441775</v>
+        <v>4.913821746482462</v>
       </c>
       <c r="D51">
-        <v>12.55464761744177</v>
+        <v>12.46482174648246</v>
       </c>
       <c r="E51">
-        <v>8.280999999999999</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="F51">
-        <v>8.280999999999999</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="G51">
         <v>0.899</v>
@@ -5457,37 +5457,37 @@
         <v>0.9379999999999999</v>
       </c>
       <c r="M51">
-        <v>1.6628248</v>
+        <v>1.69676</v>
       </c>
       <c r="N51">
-        <v>-0.7248247999999999</v>
+        <v>-0.7587599999999999</v>
       </c>
       <c r="O51">
-        <v>-0.210199192</v>
+        <v>-0.2200403999999999</v>
       </c>
       <c r="P51">
-        <v>-0.514625608</v>
+        <v>-0.5387196</v>
       </c>
       <c r="Q51">
-        <v>0.08737439200000008</v>
+        <v>0.06328040000000013</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.3501802615733757</v>
+        <v>0.3562678668048433</v>
       </c>
       <c r="T51">
-        <v>1.861551789090709</v>
+        <v>1.898782824872524</v>
       </c>
       <c r="U51">
         <v>0.2008</v>
       </c>
       <c r="V51">
-        <v>0.163589092488878</v>
+        <v>0.1603173106391004</v>
       </c>
       <c r="W51">
-        <v>0.1679513102282333</v>
+        <v>0.1686082840236686</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5495,7 +5495,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.5641003189271654</v>
+        <v>0.5528183125486221</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5503,22 +5503,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.262438075414256</v>
+        <v>0.263988075414256</v>
       </c>
       <c r="C52">
-        <v>4.913821746482462</v>
+        <v>4.656272114838451</v>
       </c>
       <c r="D52">
-        <v>12.46482174648246</v>
+        <v>12.37627211483845</v>
       </c>
       <c r="E52">
-        <v>8.449999999999999</v>
+        <v>8.619</v>
       </c>
       <c r="F52">
-        <v>8.449999999999999</v>
+        <v>8.619</v>
       </c>
       <c r="G52">
         <v>0.899</v>
@@ -5539,37 +5539,37 @@
         <v>0.9379999999999999</v>
       </c>
       <c r="M52">
-        <v>1.69676</v>
+        <v>1.7306952</v>
       </c>
       <c r="N52">
-        <v>-0.7587599999999999</v>
+        <v>-0.7926952</v>
       </c>
       <c r="O52">
-        <v>-0.2200403999999999</v>
+        <v>-0.229881608</v>
       </c>
       <c r="P52">
-        <v>-0.5387196</v>
+        <v>-0.562813592</v>
       </c>
       <c r="Q52">
-        <v>0.06328040000000013</v>
+        <v>0.03918640800000006</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.3562678668048433</v>
+        <v>0.3626039457192278</v>
       </c>
       <c r="T52">
-        <v>1.898782824872524</v>
+        <v>1.937533494767882</v>
       </c>
       <c r="U52">
         <v>0.2008</v>
       </c>
       <c r="V52">
-        <v>0.1603173106391004</v>
+        <v>0.1571738339599023</v>
       </c>
       <c r="W52">
-        <v>0.1686082840236686</v>
+        <v>0.1692394941408516</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5577,7 +5577,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.5528183125486221</v>
+        <v>0.5419787377927667</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5585,22 +5585,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.263988075414256</v>
+        <v>0.265538075414256</v>
       </c>
       <c r="C53">
-        <v>4.656272114838451</v>
+        <v>4.399971715297607</v>
       </c>
       <c r="D53">
-        <v>12.37627211483845</v>
+        <v>12.28897171529761</v>
       </c>
       <c r="E53">
-        <v>8.619</v>
+        <v>8.788</v>
       </c>
       <c r="F53">
-        <v>8.619</v>
+        <v>8.788</v>
       </c>
       <c r="G53">
         <v>0.899</v>
@@ -5621,37 +5621,37 @@
         <v>0.9379999999999999</v>
       </c>
       <c r="M53">
-        <v>1.7306952</v>
+        <v>1.7646304</v>
       </c>
       <c r="N53">
-        <v>-0.7926952</v>
+        <v>-0.8266304000000002</v>
       </c>
       <c r="O53">
-        <v>-0.229881608</v>
+        <v>-0.239722816</v>
       </c>
       <c r="P53">
-        <v>-0.562813592</v>
+        <v>-0.5869075840000002</v>
       </c>
       <c r="Q53">
-        <v>0.03918640800000006</v>
+        <v>0.01509241599999989</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.3626039457192278</v>
+        <v>0.3692040279217118</v>
       </c>
       <c r="T53">
-        <v>1.937533494767882</v>
+        <v>1.977898775908879</v>
       </c>
       <c r="U53">
         <v>0.2008</v>
       </c>
       <c r="V53">
-        <v>0.1571738339599023</v>
+        <v>0.1541512602299042</v>
       </c>
       <c r="W53">
-        <v>0.1692394941408516</v>
+        <v>0.1698464269458352</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5659,7 +5659,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.5419787377927667</v>
+        <v>0.5315560697582904</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5667,22 +5667,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.265538075414256</v>
+        <v>0.2670880754142559</v>
       </c>
       <c r="C54">
-        <v>4.399971715297607</v>
+        <v>4.144894297329868</v>
       </c>
       <c r="D54">
-        <v>12.28897171529761</v>
+        <v>12.20289429732987</v>
       </c>
       <c r="E54">
-        <v>8.788</v>
+        <v>8.956999999999999</v>
       </c>
       <c r="F54">
-        <v>8.788</v>
+        <v>8.956999999999999</v>
       </c>
       <c r="G54">
         <v>0.899</v>
@@ -5703,37 +5703,37 @@
         <v>0.9379999999999999</v>
       </c>
       <c r="M54">
-        <v>1.7646304</v>
+        <v>1.7985656</v>
       </c>
       <c r="N54">
-        <v>-0.8266304000000002</v>
+        <v>-0.8605655999999999</v>
       </c>
       <c r="O54">
-        <v>-0.239722816</v>
+        <v>-0.249564024</v>
       </c>
       <c r="P54">
-        <v>-0.5869075840000002</v>
+        <v>-0.6110015759999999</v>
       </c>
       <c r="Q54">
-        <v>0.01509241599999989</v>
+        <v>-0.009001575999999845</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.3692040279217118</v>
+        <v>0.3760849646860034</v>
       </c>
       <c r="T54">
-        <v>1.977898775908879</v>
+        <v>2.019981728587791</v>
       </c>
       <c r="U54">
         <v>0.2008</v>
       </c>
       <c r="V54">
-        <v>0.1541512602299042</v>
+        <v>0.1512427458859438</v>
       </c>
       <c r="W54">
-        <v>0.1698464269458352</v>
+        <v>0.1704304566261025</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5741,7 +5741,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.5315560697582904</v>
+        <v>0.5215267099515303</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5749,22 +5749,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.2670880754142559</v>
+        <v>0.2686380754142559</v>
       </c>
       <c r="C55">
-        <v>4.144894297329868</v>
+        <v>3.891014340770832</v>
       </c>
       <c r="D55">
-        <v>12.20289429732987</v>
+        <v>12.11801434077083</v>
       </c>
       <c r="E55">
-        <v>8.956999999999999</v>
+        <v>9.125999999999999</v>
       </c>
       <c r="F55">
-        <v>8.956999999999999</v>
+        <v>9.125999999999999</v>
       </c>
       <c r="G55">
         <v>0.899</v>
@@ -5785,37 +5785,37 @@
         <v>0.9379999999999999</v>
       </c>
       <c r="M55">
-        <v>1.7985656</v>
+        <v>1.8325008</v>
       </c>
       <c r="N55">
-        <v>-0.8605655999999999</v>
+        <v>-0.8945008000000001</v>
       </c>
       <c r="O55">
-        <v>-0.249564024</v>
+        <v>-0.259405232</v>
       </c>
       <c r="P55">
-        <v>-0.6110015759999999</v>
+        <v>-0.6350955680000001</v>
       </c>
       <c r="Q55">
-        <v>-0.009001575999999845</v>
+        <v>-0.03309556800000002</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.3760849646860034</v>
+        <v>0.38326507261396</v>
       </c>
       <c r="T55">
-        <v>2.019981728587791</v>
+        <v>2.063894374861439</v>
       </c>
       <c r="U55">
         <v>0.2008</v>
       </c>
       <c r="V55">
-        <v>0.1512427458859438</v>
+        <v>0.1484419542954633</v>
       </c>
       <c r="W55">
-        <v>0.1704304566261025</v>
+        <v>0.170992855577471</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5823,7 +5823,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.5215267099515303</v>
+        <v>0.5118688079153908</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5831,22 +5831,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.2686380754142559</v>
+        <v>0.2701880754142559</v>
       </c>
       <c r="C56">
-        <v>3.891014340770832</v>
+        <v>3.638307030596176</v>
       </c>
       <c r="D56">
-        <v>12.11801434077083</v>
+        <v>12.03430703059617</v>
       </c>
       <c r="E56">
-        <v>9.125999999999999</v>
+        <v>9.295</v>
       </c>
       <c r="F56">
-        <v>9.125999999999999</v>
+        <v>9.295</v>
       </c>
       <c r="G56">
         <v>0.899</v>
@@ -5867,37 +5867,37 @@
         <v>0.9379999999999999</v>
       </c>
       <c r="M56">
-        <v>1.8325008</v>
+        <v>1.866436</v>
       </c>
       <c r="N56">
-        <v>-0.8945008000000001</v>
+        <v>-0.928436</v>
       </c>
       <c r="O56">
-        <v>-0.259405232</v>
+        <v>-0.26924644</v>
       </c>
       <c r="P56">
-        <v>-0.6350955680000001</v>
+        <v>-0.6591895600000001</v>
       </c>
       <c r="Q56">
-        <v>-0.03309556800000002</v>
+        <v>-0.05718955999999997</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.38326507261396</v>
+        <v>0.3907642964498259</v>
       </c>
       <c r="T56">
-        <v>2.063894374861439</v>
+        <v>2.109758694302804</v>
       </c>
       <c r="U56">
         <v>0.2008</v>
       </c>
       <c r="V56">
-        <v>0.1484419542954633</v>
+        <v>0.1457430096719094</v>
       </c>
       <c r="W56">
-        <v>0.170992855577471</v>
+        <v>0.1715348036578806</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5905,7 +5905,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.5118688079153908</v>
+        <v>0.5025621023169291</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5913,22 +5913,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.2701880754142559</v>
+        <v>0.2933460046474917</v>
       </c>
       <c r="C57">
-        <v>3.638307030596176</v>
+        <v>2.343497583651414</v>
       </c>
       <c r="D57">
-        <v>12.03430703059617</v>
+        <v>10.90849758365141</v>
       </c>
       <c r="E57">
-        <v>9.295</v>
+        <v>9.464</v>
       </c>
       <c r="F57">
-        <v>9.295</v>
+        <v>9.464</v>
       </c>
       <c r="G57">
         <v>0.899</v>
@@ -5949,45 +5949,45 @@
         <v>0.9379999999999999</v>
       </c>
       <c r="M57">
-        <v>1.866436</v>
+        <v>2.2316112</v>
       </c>
       <c r="N57">
-        <v>-0.928436</v>
+        <v>-1.2936112</v>
       </c>
       <c r="O57">
-        <v>-0.26924644</v>
+        <v>-0.375147248</v>
       </c>
       <c r="P57">
-        <v>-0.6591895600000001</v>
+        <v>-0.9184639520000002</v>
       </c>
       <c r="Q57">
-        <v>-0.05718955999999997</v>
+        <v>-0.3164639520000001</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.3907642964498259</v>
+        <v>0.4031678696264941</v>
       </c>
       <c r="T57">
-        <v>2.109758694302804</v>
+        <v>2.185617403795957</v>
       </c>
       <c r="U57">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.1457430096719094</v>
+        <v>0.1218939930037992</v>
       </c>
       <c r="W57">
-        <v>0.1715348036578806</v>
+        <v>0.2070573964497041</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y57">
-        <v>0.5025621023169291</v>
+        <v>0.4203241138062042</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5995,22 +5995,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.2933460046474917</v>
+        <v>0.2952460046474917</v>
       </c>
       <c r="C58">
-        <v>2.343497583651414</v>
+        <v>2.09140887899075</v>
       </c>
       <c r="D58">
-        <v>10.90849758365141</v>
+        <v>10.82540887899075</v>
       </c>
       <c r="E58">
-        <v>9.464</v>
+        <v>9.633000000000001</v>
       </c>
       <c r="F58">
-        <v>9.464</v>
+        <v>9.633000000000001</v>
       </c>
       <c r="G58">
         <v>0.899</v>
@@ -6031,37 +6031,37 @@
         <v>0.9379999999999999</v>
       </c>
       <c r="M58">
-        <v>2.2316112</v>
+        <v>2.2714614</v>
       </c>
       <c r="N58">
-        <v>-1.2936112</v>
+        <v>-1.3334614</v>
       </c>
       <c r="O58">
-        <v>-0.375147248</v>
+        <v>-0.386703806</v>
       </c>
       <c r="P58">
-        <v>-0.9184639520000002</v>
+        <v>-0.9467575940000001</v>
       </c>
       <c r="Q58">
-        <v>-0.3164639520000001</v>
+        <v>-0.3447575940000001</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.4031678696264941</v>
+        <v>0.4114787503154824</v>
       </c>
       <c r="T58">
-        <v>2.185617403795957</v>
+        <v>2.236445715512142</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.1218939930037992</v>
+        <v>0.1197555018984694</v>
       </c>
       <c r="W58">
-        <v>0.2070573964497041</v>
+        <v>0.2075616526523409</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6069,7 +6069,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.4203241138062042</v>
+        <v>0.4129500065464462</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6077,22 +6077,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.2952460046474917</v>
+        <v>0.2971460046474917</v>
       </c>
       <c r="C59">
-        <v>2.09140887899075</v>
+        <v>1.840576359317605</v>
       </c>
       <c r="D59">
-        <v>10.82540887899075</v>
+        <v>10.7435763593176</v>
       </c>
       <c r="E59">
-        <v>9.633000000000001</v>
+        <v>9.802</v>
       </c>
       <c r="F59">
-        <v>9.633000000000001</v>
+        <v>9.802</v>
       </c>
       <c r="G59">
         <v>0.899</v>
@@ -6113,37 +6113,37 @@
         <v>0.9379999999999999</v>
       </c>
       <c r="M59">
-        <v>2.2714614</v>
+        <v>2.3113116</v>
       </c>
       <c r="N59">
-        <v>-1.3334614</v>
+        <v>-1.3733116</v>
       </c>
       <c r="O59">
-        <v>-0.386703806</v>
+        <v>-0.3982603639999999</v>
       </c>
       <c r="P59">
-        <v>-0.9467575940000001</v>
+        <v>-0.9750512359999999</v>
       </c>
       <c r="Q59">
-        <v>-0.3447575940000001</v>
+        <v>-0.3730512359999998</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.4114787503154824</v>
+        <v>0.4201853872277557</v>
       </c>
       <c r="T59">
-        <v>2.236445715512142</v>
+        <v>2.289694423024335</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.1197555018984694</v>
+        <v>0.1176907518657372</v>
       </c>
       <c r="W59">
-        <v>0.2075616526523409</v>
+        <v>0.2080485207100592</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6151,7 +6151,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.4129500065464462</v>
+        <v>0.4058301788473696</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6159,22 +6159,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.2971460046474917</v>
+        <v>0.2990460046474917</v>
       </c>
       <c r="C60">
-        <v>1.840576359317607</v>
+        <v>1.590971750723222</v>
       </c>
       <c r="D60">
-        <v>10.7435763593176</v>
+        <v>10.66297175072322</v>
       </c>
       <c r="E60">
-        <v>9.801999999999998</v>
+        <v>9.970999999999998</v>
       </c>
       <c r="F60">
-        <v>9.801999999999998</v>
+        <v>9.970999999999998</v>
       </c>
       <c r="G60">
         <v>0.899</v>
@@ -6195,37 +6195,37 @@
         <v>0.9379999999999999</v>
       </c>
       <c r="M60">
-        <v>2.3113116</v>
+        <v>2.3511618</v>
       </c>
       <c r="N60">
-        <v>-1.3733116</v>
+        <v>-1.4131618</v>
       </c>
       <c r="O60">
-        <v>-0.3982603639999999</v>
+        <v>-0.409816922</v>
       </c>
       <c r="P60">
-        <v>-0.9750512359999999</v>
+        <v>-1.003344878</v>
       </c>
       <c r="Q60">
-        <v>-0.3730512359999998</v>
+        <v>-0.401344878</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.4201853872277557</v>
+        <v>0.4293167381357497</v>
       </c>
       <c r="T60">
-        <v>2.289694423024335</v>
+        <v>2.345540628463953</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.1176907518657372</v>
+        <v>0.1156959933595382</v>
       </c>
       <c r="W60">
-        <v>0.2080485207100592</v>
+        <v>0.2085188847658209</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6233,7 +6233,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.4058301788473696</v>
+        <v>0.3989517012397871</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.2990460046474917</v>
+        <v>0.3009460046474918</v>
       </c>
       <c r="C61">
-        <v>1.590971750723222</v>
+        <v>1.342567621489978</v>
       </c>
       <c r="D61">
-        <v>10.66297175072322</v>
+        <v>10.58356762148998</v>
       </c>
       <c r="E61">
-        <v>9.970999999999998</v>
+        <v>10.14</v>
       </c>
       <c r="F61">
-        <v>9.970999999999998</v>
+        <v>10.14</v>
       </c>
       <c r="G61">
         <v>0.899</v>
@@ -6277,37 +6277,37 @@
         <v>0.9379999999999999</v>
       </c>
       <c r="M61">
-        <v>2.3511618</v>
+        <v>2.391012</v>
       </c>
       <c r="N61">
-        <v>-1.4131618</v>
+        <v>-1.453012</v>
       </c>
       <c r="O61">
-        <v>-0.409816922</v>
+        <v>-0.42137348</v>
       </c>
       <c r="P61">
-        <v>-1.003344878</v>
+        <v>-1.03163852</v>
       </c>
       <c r="Q61">
-        <v>-0.401344878</v>
+        <v>-0.4296385199999999</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.4293167381357497</v>
+        <v>0.4389046565891435</v>
       </c>
       <c r="T61">
-        <v>2.345540628463953</v>
+        <v>2.404179144175552</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.1156959933595382</v>
+        <v>0.1137677268035459</v>
       </c>
       <c r="W61">
-        <v>0.2085188847658209</v>
+        <v>0.2089735700197239</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6315,7 +6315,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.3989517012397871</v>
+        <v>0.392302506219124</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6323,22 +6323,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.3009460046474918</v>
+        <v>0.3028460046474917</v>
       </c>
       <c r="C62">
-        <v>1.342567621489978</v>
+        <v>1.095337350965417</v>
       </c>
       <c r="D62">
-        <v>10.58356762148998</v>
+        <v>10.50533735096542</v>
       </c>
       <c r="E62">
-        <v>10.14</v>
+        <v>10.309</v>
       </c>
       <c r="F62">
-        <v>10.14</v>
+        <v>10.309</v>
       </c>
       <c r="G62">
         <v>0.899</v>
@@ -6359,37 +6359,37 @@
         <v>0.9379999999999999</v>
       </c>
       <c r="M62">
-        <v>2.391012</v>
+        <v>2.4308622</v>
       </c>
       <c r="N62">
-        <v>-1.453012</v>
+        <v>-1.4928622</v>
       </c>
       <c r="O62">
-        <v>-0.42137348</v>
+        <v>-0.432930038</v>
       </c>
       <c r="P62">
-        <v>-1.03163852</v>
+        <v>-1.059932162</v>
       </c>
       <c r="Q62">
-        <v>-0.4296385199999999</v>
+        <v>-0.4579321619999999</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.4389046565891435</v>
+        <v>0.4489842631683523</v>
       </c>
       <c r="T62">
-        <v>2.404179144175552</v>
+        <v>2.465824763256977</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.1137677268035459</v>
+        <v>0.1119026821018485</v>
       </c>
       <c r="W62">
-        <v>0.2089735700197239</v>
+        <v>0.2094133475603841</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6397,7 +6397,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.392302506219124</v>
+        <v>0.3858713175925809</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6405,22 +6405,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.3028460046474917</v>
+        <v>0.3047460046474917</v>
       </c>
       <c r="C63">
-        <v>1.095337350965417</v>
+        <v>0.8492550998065109</v>
       </c>
       <c r="D63">
-        <v>10.50533735096542</v>
+        <v>10.42825509980651</v>
       </c>
       <c r="E63">
-        <v>10.309</v>
+        <v>10.478</v>
       </c>
       <c r="F63">
-        <v>10.309</v>
+        <v>10.478</v>
       </c>
       <c r="G63">
         <v>0.899</v>
@@ -6441,37 +6441,37 @@
         <v>0.9379999999999999</v>
       </c>
       <c r="M63">
-        <v>2.4308622</v>
+        <v>2.4707124</v>
       </c>
       <c r="N63">
-        <v>-1.4928622</v>
+        <v>-1.5327124</v>
       </c>
       <c r="O63">
-        <v>-0.432930038</v>
+        <v>-0.444486596</v>
       </c>
       <c r="P63">
-        <v>-1.059932162</v>
+        <v>-1.088225804</v>
       </c>
       <c r="Q63">
-        <v>-0.4579321619999999</v>
+        <v>-0.486225804</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.4489842631683523</v>
+        <v>0.4595943753569932</v>
       </c>
       <c r="T63">
-        <v>2.465824763256977</v>
+        <v>2.530714888605844</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.1119026821018485</v>
+        <v>0.1100978001324638</v>
       </c>
       <c r="W63">
-        <v>0.2094133475603841</v>
+        <v>0.209838938728765</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6479,7 +6479,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.3858713175925809</v>
+        <v>0.3796475866636683</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6487,22 +6487,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.3047460046474917</v>
+        <v>0.3066460046474917</v>
       </c>
       <c r="C64">
-        <v>0.8492550998065109</v>
+        <v>0.6042957815244101</v>
       </c>
       <c r="D64">
-        <v>10.42825509980651</v>
+        <v>10.35229578152441</v>
       </c>
       <c r="E64">
-        <v>10.478</v>
+        <v>10.647</v>
       </c>
       <c r="F64">
-        <v>10.478</v>
+        <v>10.647</v>
       </c>
       <c r="G64">
         <v>0.899</v>
@@ -6523,37 +6523,37 @@
         <v>0.9379999999999999</v>
       </c>
       <c r="M64">
-        <v>2.4707124</v>
+        <v>2.5105626</v>
       </c>
       <c r="N64">
-        <v>-1.5327124</v>
+        <v>-1.5725626</v>
       </c>
       <c r="O64">
-        <v>-0.444486596</v>
+        <v>-0.4560431539999999</v>
       </c>
       <c r="P64">
-        <v>-1.088225804</v>
+        <v>-1.116519446</v>
       </c>
       <c r="Q64">
-        <v>-0.486225804</v>
+        <v>-0.5145194459999998</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.4595943753569932</v>
+        <v>0.4707780071233983</v>
       </c>
       <c r="T64">
-        <v>2.530714888605844</v>
+        <v>2.599112588297894</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.1100978001324638</v>
+        <v>0.1083502160033771</v>
       </c>
       <c r="W64">
-        <v>0.209838938728765</v>
+        <v>0.2102510190664037</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.3796475866636683</v>
+        <v>0.3736214344944038</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6569,22 +6569,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.3066460046474917</v>
+        <v>0.3085460046474917</v>
       </c>
       <c r="C65">
-        <v>0.6042957815244101</v>
+        <v>0.3604350352638335</v>
       </c>
       <c r="D65">
-        <v>10.35229578152441</v>
+        <v>10.27743503526383</v>
       </c>
       <c r="E65">
-        <v>10.647</v>
+        <v>10.816</v>
       </c>
       <c r="F65">
-        <v>10.647</v>
+        <v>10.816</v>
       </c>
       <c r="G65">
         <v>0.899</v>
@@ -6605,37 +6605,37 @@
         <v>0.9379999999999999</v>
       </c>
       <c r="M65">
-        <v>2.5105626</v>
+        <v>2.5504128</v>
       </c>
       <c r="N65">
-        <v>-1.5725626</v>
+        <v>-1.6124128</v>
       </c>
       <c r="O65">
-        <v>-0.4560431539999999</v>
+        <v>-0.4675997119999999</v>
       </c>
       <c r="P65">
-        <v>-1.116519446</v>
+        <v>-1.144813088</v>
       </c>
       <c r="Q65">
-        <v>-0.5145194459999998</v>
+        <v>-0.5428130879999997</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.4707780071233983</v>
+        <v>0.482582951765715</v>
       </c>
       <c r="T65">
-        <v>2.599112588297894</v>
+        <v>2.671310160195058</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.1083502160033771</v>
+        <v>0.1066572438783243</v>
       </c>
       <c r="W65">
-        <v>0.2102510190664037</v>
+        <v>0.2106502218934911</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6643,7 +6643,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.3736214344944038</v>
+        <v>0.3677835995804287</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6651,22 +6651,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.3085460046474917</v>
+        <v>0.3104460046474917</v>
       </c>
       <c r="C66">
-        <v>0.3604350352638335</v>
+        <v>0.1176491997549576</v>
       </c>
       <c r="D66">
-        <v>10.27743503526383</v>
+        <v>10.20364919975496</v>
       </c>
       <c r="E66">
-        <v>10.816</v>
+        <v>10.985</v>
       </c>
       <c r="F66">
-        <v>10.816</v>
+        <v>10.985</v>
       </c>
       <c r="G66">
         <v>0.899</v>
@@ -6687,37 +6687,37 @@
         <v>0.9379999999999999</v>
       </c>
       <c r="M66">
-        <v>2.5504128</v>
+        <v>2.590263</v>
       </c>
       <c r="N66">
-        <v>-1.6124128</v>
+        <v>-1.652263</v>
       </c>
       <c r="O66">
-        <v>-0.4675997119999999</v>
+        <v>-0.4791562699999999</v>
       </c>
       <c r="P66">
-        <v>-1.144813088</v>
+        <v>-1.17310673</v>
       </c>
       <c r="Q66">
-        <v>-0.5428130879999997</v>
+        <v>-0.5711067299999997</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.482582951765715</v>
+        <v>0.4950624646733069</v>
       </c>
       <c r="T66">
-        <v>2.671310160195058</v>
+        <v>2.747633307629203</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.1066572438783243</v>
+        <v>0.1050163632032732</v>
       </c>
       <c r="W66">
-        <v>0.2106502218934911</v>
+        <v>0.2110371415566682</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6725,7 +6725,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.3677835995804287</v>
+        <v>0.3621253903561145</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6733,22 +6733,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.3104460046474917</v>
+        <v>0.3123460046474917</v>
       </c>
       <c r="C67">
-        <v>0.1176491997549576</v>
+        <v>-0.1240847116205828</v>
       </c>
       <c r="D67">
-        <v>10.20364919975496</v>
+        <v>10.13091528837942</v>
       </c>
       <c r="E67">
-        <v>10.985</v>
+        <v>11.154</v>
       </c>
       <c r="F67">
-        <v>10.985</v>
+        <v>11.154</v>
       </c>
       <c r="G67">
         <v>0.899</v>
@@ -6769,37 +6769,37 @@
         <v>0.9379999999999999</v>
       </c>
       <c r="M67">
-        <v>2.590263</v>
+        <v>2.6301132</v>
       </c>
       <c r="N67">
-        <v>-1.652263</v>
+        <v>-1.6921132</v>
       </c>
       <c r="O67">
-        <v>-0.4791562699999999</v>
+        <v>-0.490712828</v>
       </c>
       <c r="P67">
-        <v>-1.17310673</v>
+        <v>-1.201400372</v>
       </c>
       <c r="Q67">
-        <v>-0.5711067299999997</v>
+        <v>-0.5994003720000001</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.4950624646733069</v>
+        <v>0.508276066575463</v>
       </c>
       <c r="T67">
-        <v>2.747633307629203</v>
+        <v>2.828446051971238</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.1050163632032732</v>
+        <v>0.1034252061850418</v>
       </c>
       <c r="W67">
-        <v>0.2110371415566682</v>
+        <v>0.2114123363815671</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6807,7 +6807,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.3621253903561145</v>
+        <v>0.3566386420173854</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6815,22 +6815,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.3123460046474917</v>
+        <v>0.3142460046474918</v>
       </c>
       <c r="C68">
-        <v>-0.1240847116205828</v>
+        <v>-0.3647890347048381</v>
       </c>
       <c r="D68">
-        <v>10.13091528837942</v>
+        <v>10.05921096529516</v>
       </c>
       <c r="E68">
-        <v>11.154</v>
+        <v>11.323</v>
       </c>
       <c r="F68">
-        <v>11.154</v>
+        <v>11.323</v>
       </c>
       <c r="G68">
         <v>0.899</v>
@@ -6851,37 +6851,37 @@
         <v>0.9379999999999999</v>
       </c>
       <c r="M68">
-        <v>2.6301132</v>
+        <v>2.6699634</v>
       </c>
       <c r="N68">
-        <v>-1.6921132</v>
+        <v>-1.7319634</v>
       </c>
       <c r="O68">
-        <v>-0.490712828</v>
+        <v>-0.502269386</v>
       </c>
       <c r="P68">
-        <v>-1.201400372</v>
+        <v>-1.229694014</v>
       </c>
       <c r="Q68">
-        <v>-0.5994003720000001</v>
+        <v>-0.6276940140000002</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.508276066575463</v>
+        <v>0.5222904928353255</v>
       </c>
       <c r="T68">
-        <v>2.828446051971238</v>
+        <v>2.914156538394609</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.1034252061850418</v>
+        <v>0.1018815463912351</v>
       </c>
       <c r="W68">
-        <v>0.2114123363815671</v>
+        <v>0.2117763313609468</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6889,7 +6889,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.3566386420173854</v>
+        <v>0.3513156772111558</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6897,22 +6897,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.3142460046474918</v>
+        <v>0.3161460046474918</v>
       </c>
       <c r="C69">
-        <v>-0.3647890347048381</v>
+        <v>-0.6044854774319344</v>
       </c>
       <c r="D69">
-        <v>10.05921096529516</v>
+        <v>9.988514522568066</v>
       </c>
       <c r="E69">
-        <v>11.323</v>
+        <v>11.492</v>
       </c>
       <c r="F69">
-        <v>11.323</v>
+        <v>11.492</v>
       </c>
       <c r="G69">
         <v>0.899</v>
@@ -6933,37 +6933,37 @@
         <v>0.9379999999999999</v>
       </c>
       <c r="M69">
-        <v>2.6699634</v>
+        <v>2.7098136</v>
       </c>
       <c r="N69">
-        <v>-1.7319634</v>
+        <v>-1.7718136</v>
       </c>
       <c r="O69">
-        <v>-0.502269386</v>
+        <v>-0.5138259439999999</v>
       </c>
       <c r="P69">
-        <v>-1.229694014</v>
+        <v>-1.257987656</v>
       </c>
       <c r="Q69">
-        <v>-0.6276940140000002</v>
+        <v>-0.655987656</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.5222904928353255</v>
+        <v>0.5371808207364295</v>
       </c>
       <c r="T69">
-        <v>2.914156538394609</v>
+        <v>3.005223930219441</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.1018815463912351</v>
+        <v>0.1003832883560699</v>
       </c>
       <c r="W69">
-        <v>0.2117763313609468</v>
+        <v>0.2121296206056387</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6971,7 +6971,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.3513156772111558</v>
+        <v>0.3461492701933446</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6979,22 +6979,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.3161460046474918</v>
+        <v>0.3180460046474918</v>
       </c>
       <c r="C70">
-        <v>-0.6044854774319344</v>
+        <v>-0.8431951417388657</v>
       </c>
       <c r="D70">
-        <v>9.988514522568066</v>
+        <v>9.918804858261135</v>
       </c>
       <c r="E70">
-        <v>11.492</v>
+        <v>11.661</v>
       </c>
       <c r="F70">
-        <v>11.492</v>
+        <v>11.661</v>
       </c>
       <c r="G70">
         <v>0.899</v>
@@ -7015,37 +7015,37 @@
         <v>0.9379999999999999</v>
       </c>
       <c r="M70">
-        <v>2.7098136</v>
+        <v>2.7496638</v>
       </c>
       <c r="N70">
-        <v>-1.7718136</v>
+        <v>-1.8116638</v>
       </c>
       <c r="O70">
-        <v>-0.5138259439999999</v>
+        <v>-0.525382502</v>
       </c>
       <c r="P70">
-        <v>-1.257987656</v>
+        <v>-1.286281298</v>
       </c>
       <c r="Q70">
-        <v>-0.655987656</v>
+        <v>-0.6842812979999999</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.5371808207364295</v>
+        <v>0.5530318149537337</v>
       </c>
       <c r="T70">
-        <v>3.005223930219441</v>
+        <v>3.102166637645875</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.1003832883560699</v>
+        <v>0.09892845809003994</v>
       </c>
       <c r="W70">
-        <v>0.2121296206056387</v>
+        <v>0.2124726695823686</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.3461492701933446</v>
+        <v>0.341132614103586</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7061,22 +7061,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.3180460046474918</v>
+        <v>0.3199460046474917</v>
       </c>
       <c r="C71">
-        <v>-0.8431951417388657</v>
+        <v>-1.080938544565134</v>
       </c>
       <c r="D71">
-        <v>9.918804858261135</v>
+        <v>9.850061455434865</v>
       </c>
       <c r="E71">
-        <v>11.661</v>
+        <v>11.83</v>
       </c>
       <c r="F71">
-        <v>11.661</v>
+        <v>11.83</v>
       </c>
       <c r="G71">
         <v>0.899</v>
@@ -7097,37 +7097,37 @@
         <v>0.9379999999999999</v>
       </c>
       <c r="M71">
-        <v>2.7496638</v>
+        <v>2.789514</v>
       </c>
       <c r="N71">
-        <v>-1.8116638</v>
+        <v>-1.851514</v>
       </c>
       <c r="O71">
-        <v>-0.525382502</v>
+        <v>-0.53693906</v>
       </c>
       <c r="P71">
-        <v>-1.286281298</v>
+        <v>-1.31457494</v>
       </c>
       <c r="Q71">
-        <v>-0.6842812979999999</v>
+        <v>-0.7125749399999999</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.5530318149537337</v>
+        <v>0.569939542118858</v>
       </c>
       <c r="T71">
-        <v>3.102166637645875</v>
+        <v>3.20557219223407</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.09892845809003994</v>
+        <v>0.09751519440303938</v>
       </c>
       <c r="W71">
-        <v>0.2124726695823686</v>
+        <v>0.2128059171597633</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.341132614103586</v>
+        <v>0.3362592910449633</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7143,22 +7143,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.3199460046474917</v>
+        <v>0.3218460046474917</v>
       </c>
       <c r="C72">
-        <v>-1.080938544565134</v>
+        <v>-1.317735637985221</v>
       </c>
       <c r="D72">
-        <v>9.850061455434865</v>
+        <v>9.78226436201478</v>
       </c>
       <c r="E72">
-        <v>11.83</v>
+        <v>11.999</v>
       </c>
       <c r="F72">
-        <v>11.83</v>
+        <v>11.999</v>
       </c>
       <c r="G72">
         <v>0.899</v>
@@ -7179,37 +7179,37 @@
         <v>0.9379999999999999</v>
       </c>
       <c r="M72">
-        <v>2.789514</v>
+        <v>2.8293642</v>
       </c>
       <c r="N72">
-        <v>-1.851514</v>
+        <v>-1.8913642</v>
       </c>
       <c r="O72">
-        <v>-0.53693906</v>
+        <v>-0.548495618</v>
       </c>
       <c r="P72">
-        <v>-1.31457494</v>
+        <v>-1.342868582</v>
       </c>
       <c r="Q72">
-        <v>-0.7125749399999999</v>
+        <v>-0.7408685820000001</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.569939542118858</v>
+        <v>0.5880133194333015</v>
       </c>
       <c r="T72">
-        <v>3.20557219223407</v>
+        <v>3.316109164380073</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.09751519440303938</v>
+        <v>0.09614174096074303</v>
       </c>
       <c r="W72">
-        <v>0.2128059171597633</v>
+        <v>0.2131297774814568</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7217,7 +7217,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.3362592910449633</v>
+        <v>0.3315232446922174</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7225,22 +7225,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.3218460046474917</v>
+        <v>0.3237460046474917</v>
       </c>
       <c r="C73">
-        <v>-1.317735637985219</v>
+        <v>-1.553605828515209</v>
       </c>
       <c r="D73">
-        <v>9.78226436201478</v>
+        <v>9.715394171484789</v>
       </c>
       <c r="E73">
-        <v>11.999</v>
+        <v>12.168</v>
       </c>
       <c r="F73">
-        <v>11.999</v>
+        <v>12.168</v>
       </c>
       <c r="G73">
         <v>0.899</v>
@@ -7261,37 +7261,37 @@
         <v>0.9379999999999999</v>
       </c>
       <c r="M73">
-        <v>2.8293642</v>
+        <v>2.8692144</v>
       </c>
       <c r="N73">
-        <v>-1.8913642</v>
+        <v>-1.9312144</v>
       </c>
       <c r="O73">
-        <v>-0.5484956179999999</v>
+        <v>-0.5600521759999999</v>
       </c>
       <c r="P73">
-        <v>-1.342868582</v>
+        <v>-1.371162224</v>
       </c>
       <c r="Q73">
-        <v>-0.7408685819999998</v>
+        <v>-0.7691622239999998</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.5880133194333014</v>
+        <v>0.6073780808416335</v>
       </c>
       <c r="T73">
-        <v>3.316109164380072</v>
+        <v>3.434541634536503</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.09614174096074306</v>
+        <v>0.09480643900295496</v>
       </c>
       <c r="W73">
-        <v>0.2131297774814568</v>
+        <v>0.2134446416831032</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7299,7 +7299,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.3315232446922174</v>
+        <v>0.3269187551826033</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7307,22 +7307,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.3237460046474917</v>
+        <v>0.3256460046474917</v>
       </c>
       <c r="C74">
-        <v>-1.553605828515209</v>
+        <v>-1.788567995633064</v>
       </c>
       <c r="D74">
-        <v>9.715394171484789</v>
+        <v>9.649432004366934</v>
       </c>
       <c r="E74">
-        <v>12.168</v>
+        <v>12.337</v>
       </c>
       <c r="F74">
-        <v>12.168</v>
+        <v>12.337</v>
       </c>
       <c r="G74">
         <v>0.899</v>
@@ -7343,37 +7343,37 @@
         <v>0.9379999999999999</v>
       </c>
       <c r="M74">
-        <v>2.8692144</v>
+        <v>2.9090646</v>
       </c>
       <c r="N74">
-        <v>-1.9312144</v>
+        <v>-1.9710646</v>
       </c>
       <c r="O74">
-        <v>-0.5600521759999999</v>
+        <v>-0.5716087339999999</v>
       </c>
       <c r="P74">
-        <v>-1.371162224</v>
+        <v>-1.399455866</v>
       </c>
       <c r="Q74">
-        <v>-0.7691622239999998</v>
+        <v>-0.7974558659999997</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.6073780808416335</v>
+        <v>0.6281772690209533</v>
       </c>
       <c r="T74">
-        <v>3.434541634536503</v>
+        <v>3.561746880260077</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.09480643900295496</v>
+        <v>0.09350772066044871</v>
       </c>
       <c r="W74">
-        <v>0.2134446416831032</v>
+        <v>0.2137508794682662</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7381,7 +7381,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.3269187551826033</v>
+        <v>0.3224404160705129</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7389,22 +7389,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.3256460046474917</v>
+        <v>0.3275460046474917</v>
       </c>
       <c r="C75">
-        <v>-1.788567995633064</v>
+        <v>-2.022640509549403</v>
       </c>
       <c r="D75">
-        <v>9.649432004366934</v>
+        <v>9.584359490450595</v>
       </c>
       <c r="E75">
-        <v>12.337</v>
+        <v>12.506</v>
       </c>
       <c r="F75">
-        <v>12.337</v>
+        <v>12.506</v>
       </c>
       <c r="G75">
         <v>0.899</v>
@@ -7425,37 +7425,37 @@
         <v>0.9379999999999999</v>
       </c>
       <c r="M75">
-        <v>2.9090646</v>
+        <v>2.9489148</v>
       </c>
       <c r="N75">
-        <v>-1.9710646</v>
+        <v>-2.0109148</v>
       </c>
       <c r="O75">
-        <v>-0.5716087339999999</v>
+        <v>-0.583165292</v>
       </c>
       <c r="P75">
-        <v>-1.399455866</v>
+        <v>-1.427749508</v>
       </c>
       <c r="Q75">
-        <v>-0.7974558659999997</v>
+        <v>-0.8257495080000001</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.6281772690209533</v>
+        <v>0.6505763947525284</v>
       </c>
       <c r="T75">
-        <v>3.561746880260077</v>
+        <v>3.698737144885464</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.09350772066044871</v>
+        <v>0.09224410281368589</v>
       </c>
       <c r="W75">
-        <v>0.2137508794682662</v>
+        <v>0.2140488405565329</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7463,7 +7463,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.3224404160705129</v>
+        <v>0.318083113150641</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7471,22 +7471,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.3275460046474917</v>
+        <v>0.3294460046474917</v>
       </c>
       <c r="C76">
-        <v>-2.022640509549403</v>
+        <v>-2.255841248264153</v>
       </c>
       <c r="D76">
-        <v>9.584359490450595</v>
+        <v>9.520158751735845</v>
       </c>
       <c r="E76">
-        <v>12.506</v>
+        <v>12.675</v>
       </c>
       <c r="F76">
-        <v>12.506</v>
+        <v>12.675</v>
       </c>
       <c r="G76">
         <v>0.899</v>
@@ -7507,37 +7507,37 @@
         <v>0.9379999999999999</v>
       </c>
       <c r="M76">
-        <v>2.9489148</v>
+        <v>2.988765</v>
       </c>
       <c r="N76">
-        <v>-2.0109148</v>
+        <v>-2.050765</v>
       </c>
       <c r="O76">
-        <v>-0.583165292</v>
+        <v>-0.59472185</v>
       </c>
       <c r="P76">
-        <v>-1.427749508</v>
+        <v>-1.45604315</v>
       </c>
       <c r="Q76">
-        <v>-0.8257495080000001</v>
+        <v>-0.8540431500000001</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.6505763947525284</v>
+        <v>0.6747674505426295</v>
       </c>
       <c r="T76">
-        <v>3.698737144885464</v>
+        <v>3.846686630680884</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.09224410281368589</v>
+        <v>0.09101418144283674</v>
       </c>
       <c r="W76">
-        <v>0.2140488405565329</v>
+        <v>0.2143388560157791</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7545,7 +7545,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.318083113150641</v>
+        <v>0.3138420049752991</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7553,22 +7553,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.3294460046474917</v>
+        <v>0.3313460046474918</v>
       </c>
       <c r="C77">
-        <v>-2.255841248264153</v>
+        <v>-2.488187613942175</v>
       </c>
       <c r="D77">
-        <v>9.520158751735845</v>
+        <v>9.456812386057823</v>
       </c>
       <c r="E77">
-        <v>12.675</v>
+        <v>12.844</v>
       </c>
       <c r="F77">
-        <v>12.675</v>
+        <v>12.844</v>
       </c>
       <c r="G77">
         <v>0.899</v>
@@ -7589,37 +7589,37 @@
         <v>0.9379999999999999</v>
       </c>
       <c r="M77">
-        <v>2.988765</v>
+        <v>3.0286152</v>
       </c>
       <c r="N77">
-        <v>-2.050765</v>
+        <v>-2.0906152</v>
       </c>
       <c r="O77">
-        <v>-0.59472185</v>
+        <v>-0.606278408</v>
       </c>
       <c r="P77">
-        <v>-1.45604315</v>
+        <v>-1.484336792</v>
       </c>
       <c r="Q77">
-        <v>-0.8540431500000001</v>
+        <v>-0.882336792</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.6747674505426295</v>
+        <v>0.7009744276485725</v>
       </c>
       <c r="T77">
-        <v>3.846686630680884</v>
+        <v>4.006965240292588</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.09101418144283674</v>
+        <v>0.08981662642385206</v>
       </c>
       <c r="W77">
-        <v>0.2143388560157791</v>
+        <v>0.2146212394892557</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7627,7 +7627,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3138420049752991</v>
+        <v>0.3097125049098346</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7635,22 +7635,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.3313460046474918</v>
+        <v>0.3332460046474918</v>
       </c>
       <c r="C78">
-        <v>-2.488187613942175</v>
+        <v>-2.719696548639478</v>
       </c>
       <c r="D78">
-        <v>9.456812386057823</v>
+        <v>9.394303451360523</v>
       </c>
       <c r="E78">
-        <v>12.844</v>
+        <v>13.013</v>
       </c>
       <c r="F78">
-        <v>12.844</v>
+        <v>13.013</v>
       </c>
       <c r="G78">
         <v>0.899</v>
@@ -7671,37 +7671,37 @@
         <v>0.9379999999999999</v>
       </c>
       <c r="M78">
-        <v>3.0286152</v>
+        <v>3.0684654</v>
       </c>
       <c r="N78">
-        <v>-2.0906152</v>
+        <v>-2.1304654</v>
       </c>
       <c r="O78">
-        <v>-0.606278408</v>
+        <v>-0.617834966</v>
       </c>
       <c r="P78">
-        <v>-1.484336792</v>
+        <v>-1.512630434</v>
       </c>
       <c r="Q78">
-        <v>-0.882336792</v>
+        <v>-0.9106304340000002</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.7009744276485725</v>
+        <v>0.7294602723289453</v>
       </c>
       <c r="T78">
-        <v>4.006965240292588</v>
+        <v>4.181181120305308</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.08981662642385206</v>
+        <v>0.08865017673003578</v>
       </c>
       <c r="W78">
-        <v>0.2146212394892557</v>
+        <v>0.2148962883270576</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3097125049098346</v>
+        <v>0.3056902645863303</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7717,22 +7717,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.3332460046474918</v>
+        <v>0.3351460046474918</v>
       </c>
       <c r="C79">
-        <v>-2.719696548639478</v>
+        <v>-2.950384549409801</v>
       </c>
       <c r="D79">
-        <v>9.394303451360523</v>
+        <v>9.332615450590199</v>
       </c>
       <c r="E79">
-        <v>13.013</v>
+        <v>13.182</v>
       </c>
       <c r="F79">
-        <v>13.013</v>
+        <v>13.182</v>
       </c>
       <c r="G79">
         <v>0.899</v>
@@ -7753,37 +7753,37 @@
         <v>0.9379999999999999</v>
       </c>
       <c r="M79">
-        <v>3.0684654</v>
+        <v>3.1083156</v>
       </c>
       <c r="N79">
-        <v>-2.1304654</v>
+        <v>-2.170315599999999</v>
       </c>
       <c r="O79">
-        <v>-0.617834966</v>
+        <v>-0.6293915239999998</v>
       </c>
       <c r="P79">
-        <v>-1.512630434</v>
+        <v>-1.540924076</v>
       </c>
       <c r="Q79">
-        <v>-0.9106304340000002</v>
+        <v>-0.9389240759999995</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.7294602723289453</v>
+        <v>0.7605357392529882</v>
       </c>
       <c r="T79">
-        <v>4.181181120305308</v>
+        <v>4.371234807591914</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.08865017673003578</v>
+        <v>0.08751363600272764</v>
       </c>
       <c r="W79">
-        <v>0.2148962883270576</v>
+        <v>0.2151642846305568</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7791,7 +7791,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3056902645863303</v>
+        <v>0.3017711586300954</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7799,22 +7799,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.3351460046474918</v>
+        <v>0.3370460046474917</v>
       </c>
       <c r="C80">
-        <v>-2.950384549409801</v>
+        <v>-3.180267682819935</v>
       </c>
       <c r="D80">
-        <v>9.332615450590199</v>
+        <v>9.271732317180065</v>
       </c>
       <c r="E80">
-        <v>13.182</v>
+        <v>13.351</v>
       </c>
       <c r="F80">
-        <v>13.182</v>
+        <v>13.351</v>
       </c>
       <c r="G80">
         <v>0.899</v>
@@ -7835,37 +7835,37 @@
         <v>0.9379999999999999</v>
       </c>
       <c r="M80">
-        <v>3.1083156</v>
+        <v>3.1481658</v>
       </c>
       <c r="N80">
-        <v>-2.170315599999999</v>
+        <v>-2.2101658</v>
       </c>
       <c r="O80">
-        <v>-0.6293915239999998</v>
+        <v>-0.6409480820000001</v>
       </c>
       <c r="P80">
-        <v>-1.540924076</v>
+        <v>-1.569217718</v>
       </c>
       <c r="Q80">
-        <v>-0.9389240759999995</v>
+        <v>-0.9672177180000003</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.7605357392529882</v>
+        <v>0.7945707744555116</v>
       </c>
       <c r="T80">
-        <v>4.371234807591914</v>
+        <v>4.579388846048672</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.08751363600272764</v>
+        <v>0.08640586845838931</v>
       </c>
       <c r="W80">
-        <v>0.2151642846305568</v>
+        <v>0.2154254962175118</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7873,7 +7873,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3017711586300954</v>
+        <v>0.29795127054617</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7881,22 +7881,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.3370460046474917</v>
+        <v>0.3389460046474917</v>
       </c>
       <c r="C81">
-        <v>-3.180267682819935</v>
+        <v>-3.409361598900507</v>
       </c>
       <c r="D81">
-        <v>9.271732317180065</v>
+        <v>9.211638401099492</v>
       </c>
       <c r="E81">
-        <v>13.351</v>
+        <v>13.52</v>
       </c>
       <c r="F81">
-        <v>13.351</v>
+        <v>13.52</v>
       </c>
       <c r="G81">
         <v>0.899</v>
@@ -7917,37 +7917,37 @@
         <v>0.9379999999999999</v>
       </c>
       <c r="M81">
-        <v>3.1481658</v>
+        <v>3.188016</v>
       </c>
       <c r="N81">
-        <v>-2.2101658</v>
+        <v>-2.250016</v>
       </c>
       <c r="O81">
-        <v>-0.6409480820000001</v>
+        <v>-0.6525046400000001</v>
       </c>
       <c r="P81">
-        <v>-1.569217718</v>
+        <v>-1.59751136</v>
       </c>
       <c r="Q81">
-        <v>-0.9672177180000003</v>
+        <v>-0.9955113600000003</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.7945707744555116</v>
+        <v>0.8320093131782871</v>
       </c>
       <c r="T81">
-        <v>4.579388846048672</v>
+        <v>4.808358288351105</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.08640586845838931</v>
+        <v>0.08532579510265943</v>
       </c>
       <c r="W81">
-        <v>0.2154254962175118</v>
+        <v>0.2156801775147929</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.29795127054617</v>
+        <v>0.2942268796643429</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7963,22 +7963,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.3389460046474917</v>
+        <v>0.3408460046474917</v>
       </c>
       <c r="C82">
-        <v>-3.409361598900507</v>
+        <v>-3.637681544557793</v>
       </c>
       <c r="D82">
-        <v>9.211638401099492</v>
+        <v>9.152318455442206</v>
       </c>
       <c r="E82">
-        <v>13.52</v>
+        <v>13.689</v>
       </c>
       <c r="F82">
-        <v>13.52</v>
+        <v>13.689</v>
       </c>
       <c r="G82">
         <v>0.899</v>
@@ -7999,37 +7999,37 @@
         <v>0.9379999999999999</v>
       </c>
       <c r="M82">
-        <v>3.188016</v>
+        <v>3.2278662</v>
       </c>
       <c r="N82">
-        <v>-2.250016</v>
+        <v>-2.289866200000001</v>
       </c>
       <c r="O82">
-        <v>-0.6525046400000001</v>
+        <v>-0.6640611980000001</v>
       </c>
       <c r="P82">
-        <v>-1.59751136</v>
+        <v>-1.625805002</v>
       </c>
       <c r="Q82">
-        <v>-0.9955113600000003</v>
+        <v>-1.023805002</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.8320093131782871</v>
+        <v>0.8733887507139865</v>
       </c>
       <c r="T82">
-        <v>4.808358288351105</v>
+        <v>5.06142977721169</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.08532579510265943</v>
+        <v>0.08427239022484884</v>
       </c>
       <c r="W82">
-        <v>0.2156801775147929</v>
+        <v>0.2159285703849807</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8037,7 +8037,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.2942268796643429</v>
+        <v>0.2905944490512028</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8045,22 +8045,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.3408460046474917</v>
+        <v>0.3427460046474917</v>
       </c>
       <c r="C83">
-        <v>-3.637681544557793</v>
+        <v>-3.865242376470601</v>
       </c>
       <c r="D83">
-        <v>9.152318455442206</v>
+        <v>9.093757623529401</v>
       </c>
       <c r="E83">
-        <v>13.689</v>
+        <v>13.858</v>
       </c>
       <c r="F83">
-        <v>13.689</v>
+        <v>13.858</v>
       </c>
       <c r="G83">
         <v>0.899</v>
@@ -8081,37 +8081,37 @@
         <v>0.9379999999999999</v>
       </c>
       <c r="M83">
-        <v>3.2278662</v>
+        <v>3.2677164</v>
       </c>
       <c r="N83">
-        <v>-2.289866200000001</v>
+        <v>-2.329716400000001</v>
       </c>
       <c r="O83">
-        <v>-0.6640611980000001</v>
+        <v>-0.6756177560000001</v>
       </c>
       <c r="P83">
-        <v>-1.625805002</v>
+        <v>-1.654098644000001</v>
       </c>
       <c r="Q83">
-        <v>-1.023805002</v>
+        <v>-1.052098644</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.8733887507139865</v>
+        <v>0.9193659035314303</v>
       </c>
       <c r="T83">
-        <v>5.06142977721169</v>
+        <v>5.342620320390118</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.08427239022484884</v>
+        <v>0.08324467814893603</v>
       </c>
       <c r="W83">
-        <v>0.2159285703849807</v>
+        <v>0.2161709048924809</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8119,7 +8119,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.2905944490512028</v>
+        <v>0.287050614306676</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8127,22 +8127,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.3427460046474917</v>
+        <v>0.3446460046474917</v>
       </c>
       <c r="C84">
-        <v>-3.865242376470601</v>
+        <v>-4.092058573495171</v>
       </c>
       <c r="D84">
-        <v>9.093757623529401</v>
+        <v>9.035941426504829</v>
       </c>
       <c r="E84">
-        <v>13.858</v>
+        <v>14.027</v>
       </c>
       <c r="F84">
-        <v>13.858</v>
+        <v>14.027</v>
       </c>
       <c r="G84">
         <v>0.899</v>
@@ -8163,37 +8163,37 @@
         <v>0.9379999999999999</v>
       </c>
       <c r="M84">
-        <v>3.2677164</v>
+        <v>3.3075666</v>
       </c>
       <c r="N84">
-        <v>-2.329716400000001</v>
+        <v>-2.3695666</v>
       </c>
       <c r="O84">
-        <v>-0.6756177560000001</v>
+        <v>-0.6871743139999998</v>
       </c>
       <c r="P84">
-        <v>-1.654098644000001</v>
+        <v>-1.682392286</v>
       </c>
       <c r="Q84">
-        <v>-1.052098644</v>
+        <v>-1.080392286</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.9193659035314303</v>
+        <v>0.9707521331509262</v>
       </c>
       <c r="T84">
-        <v>5.342620320390118</v>
+        <v>5.656892103942478</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.08324467814893603</v>
+        <v>0.08224173021943079</v>
       </c>
       <c r="W84">
-        <v>0.2161709048924809</v>
+        <v>0.2164074000142582</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.287050614306676</v>
+        <v>0.2835921731704512</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8209,22 +8209,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.3446460046474917</v>
+        <v>0.3465460046474917</v>
       </c>
       <c r="C85">
-        <v>-4.092058573495171</v>
+        <v>-4.318144248599923</v>
       </c>
       <c r="D85">
-        <v>9.035941426504829</v>
+        <v>8.978855751400076</v>
       </c>
       <c r="E85">
-        <v>14.027</v>
+        <v>14.196</v>
       </c>
       <c r="F85">
-        <v>14.027</v>
+        <v>14.196</v>
       </c>
       <c r="G85">
         <v>0.899</v>
@@ -8245,37 +8245,37 @@
         <v>0.9379999999999999</v>
       </c>
       <c r="M85">
-        <v>3.3075666</v>
+        <v>3.3474168</v>
       </c>
       <c r="N85">
-        <v>-2.3695666</v>
+        <v>-2.4094168</v>
       </c>
       <c r="O85">
-        <v>-0.6871743139999998</v>
+        <v>-0.6987308719999999</v>
       </c>
       <c r="P85">
-        <v>-1.682392286</v>
+        <v>-1.710685928</v>
       </c>
       <c r="Q85">
-        <v>-1.080392286</v>
+        <v>-1.108685928</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.9707521331509262</v>
+        <v>1.028561641472859</v>
       </c>
       <c r="T85">
-        <v>5.656892103942478</v>
+        <v>6.010447860438884</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.08224173021943079</v>
+        <v>0.08126266200253282</v>
       </c>
       <c r="W85">
-        <v>0.2164074000142582</v>
+        <v>0.2166382642998028</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.2835921731704512</v>
+        <v>0.2802160758708029</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8291,22 +8291,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.3465460046474917</v>
+        <v>0.3484460046474918</v>
       </c>
       <c r="C86">
-        <v>-4.318144248599921</v>
+        <v>-4.543513160350571</v>
       </c>
       <c r="D86">
-        <v>8.978855751400076</v>
+        <v>8.922486839649428</v>
       </c>
       <c r="E86">
-        <v>14.196</v>
+        <v>14.365</v>
       </c>
       <c r="F86">
-        <v>14.196</v>
+        <v>14.365</v>
       </c>
       <c r="G86">
         <v>0.899</v>
@@ -8327,37 +8327,37 @@
         <v>0.9379999999999999</v>
       </c>
       <c r="M86">
-        <v>3.3474168</v>
+        <v>3.387267</v>
       </c>
       <c r="N86">
-        <v>-2.4094168</v>
+        <v>-2.449267</v>
       </c>
       <c r="O86">
-        <v>-0.6987308719999999</v>
+        <v>-0.7102874299999999</v>
       </c>
       <c r="P86">
-        <v>-1.710685928</v>
+        <v>-1.73897957</v>
       </c>
       <c r="Q86">
-        <v>-1.108685928</v>
+        <v>-1.13697957</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>1.028561641472859</v>
+        <v>1.094079084237716</v>
       </c>
       <c r="T86">
-        <v>6.010447860438879</v>
+        <v>6.411144384468138</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.08126266200253282</v>
+        <v>0.08030663068485597</v>
       </c>
       <c r="W86">
-        <v>0.2166382642998028</v>
+        <v>0.216863696484511</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8365,7 +8365,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.2802160758708028</v>
+        <v>0.2769194161546756</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8373,22 +8373,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.3484460046474918</v>
+        <v>0.3503460046474918</v>
       </c>
       <c r="C87">
-        <v>-4.543513160350571</v>
+        <v>-4.768178723965356</v>
       </c>
       <c r="D87">
-        <v>8.922486839649428</v>
+        <v>8.866821276034642</v>
       </c>
       <c r="E87">
-        <v>14.365</v>
+        <v>14.534</v>
       </c>
       <c r="F87">
-        <v>14.365</v>
+        <v>14.534</v>
       </c>
       <c r="G87">
         <v>0.899</v>
@@ -8409,37 +8409,37 @@
         <v>0.9379999999999999</v>
       </c>
       <c r="M87">
-        <v>3.387267</v>
+        <v>3.4271172</v>
       </c>
       <c r="N87">
-        <v>-2.449267</v>
+        <v>-2.4891172</v>
       </c>
       <c r="O87">
-        <v>-0.7102874299999999</v>
+        <v>-0.7218439879999999</v>
       </c>
       <c r="P87">
-        <v>-1.73897957</v>
+        <v>-1.767273212</v>
       </c>
       <c r="Q87">
-        <v>-1.13697957</v>
+        <v>-1.165273212</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>1.094079084237716</v>
+        <v>1.168956161683267</v>
       </c>
       <c r="T87">
-        <v>6.411144384468138</v>
+        <v>6.869083269073005</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.08030663068485597</v>
+        <v>0.0793728326536367</v>
       </c>
       <c r="W87">
-        <v>0.216863696484511</v>
+        <v>0.2170838860602725</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.2769194161546756</v>
+        <v>0.2736994229435749</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8455,22 +8455,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.3503460046474918</v>
+        <v>0.3522460046474918</v>
       </c>
       <c r="C88">
-        <v>-4.768178723965356</v>
+        <v>-4.992154021959031</v>
       </c>
       <c r="D88">
-        <v>8.866821276034642</v>
+        <v>8.811845978040969</v>
       </c>
       <c r="E88">
-        <v>14.534</v>
+        <v>14.703</v>
       </c>
       <c r="F88">
-        <v>14.534</v>
+        <v>14.703</v>
       </c>
       <c r="G88">
         <v>0.899</v>
@@ -8491,37 +8491,37 @@
         <v>0.9379999999999999</v>
       </c>
       <c r="M88">
-        <v>3.4271172</v>
+        <v>3.4669674</v>
       </c>
       <c r="N88">
-        <v>-2.4891172</v>
+        <v>-2.5289674</v>
       </c>
       <c r="O88">
-        <v>-0.7218439879999999</v>
+        <v>-0.7334005459999999</v>
       </c>
       <c r="P88">
-        <v>-1.767273212</v>
+        <v>-1.795566854</v>
       </c>
       <c r="Q88">
-        <v>-1.165273212</v>
+        <v>-1.193566854</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>1.168956161683267</v>
+        <v>1.255352789505057</v>
       </c>
       <c r="T88">
-        <v>6.869083269073005</v>
+        <v>7.397474289770929</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.0793728326536367</v>
+        <v>0.07846050124382477</v>
       </c>
       <c r="W88">
-        <v>0.2170838860602725</v>
+        <v>0.2172990138067061</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2736994229435749</v>
+        <v>0.2705534525649131</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8537,22 +8537,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.3522460046474918</v>
+        <v>0.3541460046474918</v>
       </c>
       <c r="C89">
-        <v>-4.992154021959031</v>
+        <v>-5.215451814393271</v>
       </c>
       <c r="D89">
-        <v>8.811845978040969</v>
+        <v>8.757548185606726</v>
       </c>
       <c r="E89">
-        <v>14.703</v>
+        <v>14.872</v>
       </c>
       <c r="F89">
-        <v>14.703</v>
+        <v>14.872</v>
       </c>
       <c r="G89">
         <v>0.899</v>
@@ -8573,37 +8573,37 @@
         <v>0.9379999999999999</v>
       </c>
       <c r="M89">
-        <v>3.4669674</v>
+        <v>3.5068176</v>
       </c>
       <c r="N89">
-        <v>-2.5289674</v>
+        <v>-2.5688176</v>
       </c>
       <c r="O89">
-        <v>-0.7334005459999999</v>
+        <v>-0.7449571039999999</v>
       </c>
       <c r="P89">
-        <v>-1.795566854</v>
+        <v>-1.823860496</v>
       </c>
       <c r="Q89">
-        <v>-1.193566854</v>
+        <v>-1.221860496</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>1.255352789505057</v>
+        <v>1.356148855297145</v>
       </c>
       <c r="T89">
-        <v>7.397474289770929</v>
+        <v>8.013930480585175</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.07846050124382477</v>
+        <v>0.07756890463878133</v>
       </c>
       <c r="W89">
-        <v>0.2172990138067061</v>
+        <v>0.2175092522861754</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8611,7 +8611,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2705534525649131</v>
+        <v>0.2674789815130389</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8619,22 +8619,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.3541460046474918</v>
+        <v>0.3560460046474917</v>
       </c>
       <c r="C90">
-        <v>-5.215451814393271</v>
+        <v>-5.438084548750508</v>
       </c>
       <c r="D90">
-        <v>8.757548185606726</v>
+        <v>8.703915451249491</v>
       </c>
       <c r="E90">
-        <v>14.872</v>
+        <v>15.041</v>
       </c>
       <c r="F90">
-        <v>14.872</v>
+        <v>15.041</v>
       </c>
       <c r="G90">
         <v>0.899</v>
@@ -8655,37 +8655,37 @@
         <v>0.9379999999999999</v>
       </c>
       <c r="M90">
-        <v>3.5068176</v>
+        <v>3.5466678</v>
       </c>
       <c r="N90">
-        <v>-2.5688176</v>
+        <v>-2.6086678</v>
       </c>
       <c r="O90">
-        <v>-0.7449571039999999</v>
+        <v>-0.7565136619999999</v>
       </c>
       <c r="P90">
-        <v>-1.823860496</v>
+        <v>-1.852154138</v>
       </c>
       <c r="Q90">
-        <v>-1.221860496</v>
+        <v>-1.250154138</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>1.356148855297145</v>
+        <v>1.475271478505977</v>
       </c>
       <c r="T90">
-        <v>8.013930480585175</v>
+        <v>8.742469615183827</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.07756890463878133</v>
+        <v>0.07669734391250288</v>
       </c>
       <c r="W90">
-        <v>0.2175092522861754</v>
+        <v>0.2177147663054318</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8693,7 +8693,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2674789815130389</v>
+        <v>0.2644735996982858</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8701,22 +8701,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.3560460046474917</v>
+        <v>0.3579460046474918</v>
       </c>
       <c r="C91">
-        <v>-5.438084548750508</v>
+        <v>-5.660064369447076</v>
       </c>
       <c r="D91">
-        <v>8.703915451249491</v>
+        <v>8.650935630552922</v>
       </c>
       <c r="E91">
-        <v>15.041</v>
+        <v>15.21</v>
       </c>
       <c r="F91">
-        <v>15.041</v>
+        <v>15.21</v>
       </c>
       <c r="G91">
         <v>0.899</v>
@@ -8737,37 +8737,37 @@
         <v>0.9379999999999999</v>
       </c>
       <c r="M91">
-        <v>3.5466678</v>
+        <v>3.586518</v>
       </c>
       <c r="N91">
-        <v>-2.6086678</v>
+        <v>-2.648518</v>
       </c>
       <c r="O91">
-        <v>-0.7565136619999999</v>
+        <v>-0.76807022</v>
       </c>
       <c r="P91">
-        <v>-1.852154138</v>
+        <v>-1.88044778</v>
       </c>
       <c r="Q91">
-        <v>-1.250154138</v>
+        <v>-1.27844778</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>1.475271478505977</v>
+        <v>1.618218626356575</v>
       </c>
       <c r="T91">
-        <v>8.742469615183827</v>
+        <v>9.616716576702212</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.07669734391250288</v>
+        <v>0.07584515120236394</v>
       </c>
       <c r="W91">
-        <v>0.2177147663054318</v>
+        <v>0.2179157133464826</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8775,7 +8775,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2644735996982858</v>
+        <v>0.2615350041460826</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8783,22 +8783,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.3579460046474918</v>
+        <v>0.3598460046474917</v>
       </c>
       <c r="C92">
-        <v>-5.660064369447076</v>
+        <v>-5.881403127001084</v>
       </c>
       <c r="D92">
-        <v>8.650935630552922</v>
+        <v>8.598596872998915</v>
       </c>
       <c r="E92">
-        <v>15.21</v>
+        <v>15.379</v>
       </c>
       <c r="F92">
-        <v>15.21</v>
+        <v>15.379</v>
       </c>
       <c r="G92">
         <v>0.899</v>
@@ -8819,37 +8819,37 @@
         <v>0.9379999999999999</v>
       </c>
       <c r="M92">
-        <v>3.586518</v>
+        <v>3.6263682</v>
       </c>
       <c r="N92">
-        <v>-2.648518</v>
+        <v>-2.6883682</v>
       </c>
       <c r="O92">
-        <v>-0.76807022</v>
+        <v>-0.779626778</v>
       </c>
       <c r="P92">
-        <v>-1.88044778</v>
+        <v>-1.908741422</v>
       </c>
       <c r="Q92">
-        <v>-1.27844778</v>
+        <v>-1.306741422</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>1.618218626356575</v>
+        <v>1.792931807062861</v>
       </c>
       <c r="T92">
-        <v>9.616716576702212</v>
+        <v>10.68524064078024</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.07584515120236394</v>
+        <v>0.07501168800233798</v>
       </c>
       <c r="W92">
-        <v>0.2179157133464826</v>
+        <v>0.2181122439690487</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8857,7 +8857,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2615350041460826</v>
+        <v>0.2586609931115103</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8865,22 +8865,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.3598460046474917</v>
+        <v>0.3617460046474918</v>
       </c>
       <c r="C93">
-        <v>-5.881403127001084</v>
+        <v>-6.10211238686948</v>
       </c>
       <c r="D93">
-        <v>8.598596872998915</v>
+        <v>8.546887613130519</v>
       </c>
       <c r="E93">
-        <v>15.379</v>
+        <v>15.548</v>
       </c>
       <c r="F93">
-        <v>15.379</v>
+        <v>15.548</v>
       </c>
       <c r="G93">
         <v>0.899</v>
@@ -8901,37 +8901,37 @@
         <v>0.9379999999999999</v>
       </c>
       <c r="M93">
-        <v>3.6263682</v>
+        <v>3.6662184</v>
       </c>
       <c r="N93">
-        <v>-2.6883682</v>
+        <v>-2.7282184</v>
       </c>
       <c r="O93">
-        <v>-0.779626778</v>
+        <v>-0.791183336</v>
       </c>
       <c r="P93">
-        <v>-1.908741422</v>
+        <v>-1.937035064</v>
       </c>
       <c r="Q93">
-        <v>-1.306741422</v>
+        <v>-1.335035064</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>1.792931807062861</v>
+        <v>2.011323282945719</v>
       </c>
       <c r="T93">
-        <v>10.68524064078024</v>
+        <v>12.02089572087777</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.07501168800233798</v>
+        <v>0.07419634356752997</v>
       </c>
       <c r="W93">
-        <v>0.2181122439690487</v>
+        <v>0.2183045021867765</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8939,7 +8939,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2586609931115103</v>
+        <v>0.2558494605776894</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8947,22 +8947,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.3617460046474918</v>
+        <v>0.3636460046474917</v>
       </c>
       <c r="C94">
-        <v>-6.10211238686948</v>
+        <v>-6.322203437968131</v>
       </c>
       <c r="D94">
-        <v>8.546887613130519</v>
+        <v>8.495796562031867</v>
       </c>
       <c r="E94">
-        <v>15.548</v>
+        <v>15.717</v>
       </c>
       <c r="F94">
-        <v>15.548</v>
+        <v>15.717</v>
       </c>
       <c r="G94">
         <v>0.899</v>
@@ -8983,37 +8983,37 @@
         <v>0.9379999999999999</v>
       </c>
       <c r="M94">
-        <v>3.6662184</v>
+        <v>3.7060686</v>
       </c>
       <c r="N94">
-        <v>-2.7282184</v>
+        <v>-2.7680686</v>
       </c>
       <c r="O94">
-        <v>-0.791183336</v>
+        <v>-0.802739894</v>
       </c>
       <c r="P94">
-        <v>-1.937035064</v>
+        <v>-1.965328706</v>
       </c>
       <c r="Q94">
-        <v>-1.335035064</v>
+        <v>-1.363328706</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>2.011323282945719</v>
+        <v>2.292112323366536</v>
       </c>
       <c r="T94">
-        <v>12.02089572087777</v>
+        <v>13.73816653814602</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.07419634356752997</v>
+        <v>0.07339853342164253</v>
       </c>
       <c r="W94">
-        <v>0.2183045021867765</v>
+        <v>0.2184926258191767</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2558494605776894</v>
+        <v>0.2530983911091121</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9029,22 +9029,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.3636460046474917</v>
+        <v>0.3655460046474918</v>
       </c>
       <c r="C95">
-        <v>-6.322203437968131</v>
+        <v>-6.541687300888192</v>
       </c>
       <c r="D95">
-        <v>8.495796562031867</v>
+        <v>8.445312699111806</v>
       </c>
       <c r="E95">
-        <v>15.717</v>
+        <v>15.886</v>
       </c>
       <c r="F95">
-        <v>15.717</v>
+        <v>15.886</v>
       </c>
       <c r="G95">
         <v>0.899</v>
@@ -9065,37 +9065,37 @@
         <v>0.9379999999999999</v>
       </c>
       <c r="M95">
-        <v>3.7060686</v>
+        <v>3.7459188</v>
       </c>
       <c r="N95">
-        <v>-2.7680686</v>
+        <v>-2.8079188</v>
       </c>
       <c r="O95">
-        <v>-0.802739894</v>
+        <v>-0.814296452</v>
       </c>
       <c r="P95">
-        <v>-1.965328706</v>
+        <v>-1.993622348</v>
       </c>
       <c r="Q95">
-        <v>-1.363328706</v>
+        <v>-1.391622348</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>2.292112323366536</v>
+        <v>2.666497710594292</v>
       </c>
       <c r="T95">
-        <v>13.73816653814602</v>
+        <v>16.02786096117036</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.07339853342164253</v>
+        <v>0.07261769795971017</v>
       </c>
       <c r="W95">
-        <v>0.2184926258191767</v>
+        <v>0.2186767468211004</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2530983911091121</v>
+        <v>0.2504058550334833</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9111,22 +9111,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.3655460046474918</v>
+        <v>0.3674460046474918</v>
       </c>
       <c r="C96">
-        <v>-6.541687300888192</v>
+        <v>-6.760574735821198</v>
       </c>
       <c r="D96">
-        <v>8.445312699111806</v>
+        <v>8.395425264178803</v>
       </c>
       <c r="E96">
-        <v>15.886</v>
+        <v>16.055</v>
       </c>
       <c r="F96">
-        <v>15.886</v>
+        <v>16.055</v>
       </c>
       <c r="G96">
         <v>0.899</v>
@@ -9147,37 +9147,37 @@
         <v>0.9379999999999999</v>
       </c>
       <c r="M96">
-        <v>3.7459188</v>
+        <v>3.785769</v>
       </c>
       <c r="N96">
-        <v>-2.8079188</v>
+        <v>-2.847769</v>
       </c>
       <c r="O96">
-        <v>-0.814296452</v>
+        <v>-0.8258530100000001</v>
       </c>
       <c r="P96">
-        <v>-1.993622348</v>
+        <v>-2.02191599</v>
       </c>
       <c r="Q96">
-        <v>-1.391622348</v>
+        <v>-1.41991599</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>2.666497710594292</v>
+        <v>3.190637252713152</v>
       </c>
       <c r="T96">
-        <v>16.02786096117036</v>
+        <v>19.23343315340444</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.07261769795971017</v>
+        <v>0.07185330113908164</v>
       </c>
       <c r="W96">
-        <v>0.2186767468211004</v>
+        <v>0.2188569915914046</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2504058550334833</v>
+        <v>0.2477700039278676</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9193,22 +9193,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.3674460046474918</v>
+        <v>0.3693460046474918</v>
       </c>
       <c r="C97">
-        <v>-6.760574735821198</v>
+        <v>-6.978876250204969</v>
       </c>
       <c r="D97">
-        <v>8.395425264178803</v>
+        <v>8.34612374979503</v>
       </c>
       <c r="E97">
-        <v>16.055</v>
+        <v>16.224</v>
       </c>
       <c r="F97">
-        <v>16.055</v>
+        <v>16.224</v>
       </c>
       <c r="G97">
         <v>0.899</v>
@@ -9229,37 +9229,37 @@
         <v>0.9379999999999999</v>
       </c>
       <c r="M97">
-        <v>3.785769</v>
+        <v>3.8256192</v>
       </c>
       <c r="N97">
-        <v>-2.847769</v>
+        <v>-2.8876192</v>
       </c>
       <c r="O97">
-        <v>-0.8258530100000001</v>
+        <v>-0.8374095680000001</v>
       </c>
       <c r="P97">
-        <v>-2.02191599</v>
+        <v>-2.050209632000001</v>
       </c>
       <c r="Q97">
-        <v>-1.41991599</v>
+        <v>-1.448209632</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>3.190637252713152</v>
+        <v>3.976846565891442</v>
       </c>
       <c r="T97">
-        <v>19.23343315340444</v>
+        <v>24.04179144175557</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.07185330113908164</v>
+        <v>0.0711048292522162</v>
       </c>
       <c r="W97">
-        <v>0.2188569915914046</v>
+        <v>0.2190334812623274</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2477700039278676</v>
+        <v>0.2451890663869524</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9275,22 +9275,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.3693460046474917</v>
+        <v>0.3712460046474917</v>
       </c>
       <c r="C98">
-        <v>-6.978876250204962</v>
+        <v>-7.196602106101665</v>
       </c>
       <c r="D98">
-        <v>8.346123749795034</v>
+        <v>8.297397893898333</v>
       </c>
       <c r="E98">
-        <v>16.224</v>
+        <v>16.393</v>
       </c>
       <c r="F98">
-        <v>16.224</v>
+        <v>16.393</v>
       </c>
       <c r="G98">
         <v>0.899</v>
@@ -9311,37 +9311,37 @@
         <v>0.9379999999999999</v>
       </c>
       <c r="M98">
-        <v>3.825619199999999</v>
+        <v>3.865469399999999</v>
       </c>
       <c r="N98">
-        <v>-2.8876192</v>
+        <v>-2.9274694</v>
       </c>
       <c r="O98">
-        <v>-0.8374095679999999</v>
+        <v>-0.8489661259999999</v>
       </c>
       <c r="P98">
-        <v>-2.050209632</v>
+        <v>-2.078503274</v>
       </c>
       <c r="Q98">
-        <v>-1.448209632</v>
+        <v>-1.476503274</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>3.976846565891431</v>
+        <v>5.287195421188576</v>
       </c>
       <c r="T98">
-        <v>24.0417914417555</v>
+        <v>32.05572192234067</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.07110482925221623</v>
+        <v>0.07037178977538924</v>
       </c>
       <c r="W98">
-        <v>0.2190334812623274</v>
+        <v>0.2192063319709632</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9349,7 +9349,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2451890663869525</v>
+        <v>0.2426613440530663</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9357,22 +9357,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.3712460046474917</v>
+        <v>0.3731460046474918</v>
       </c>
       <c r="C99">
-        <v>-7.196602106101665</v>
+        <v>-7.413762327318917</v>
       </c>
       <c r="D99">
-        <v>8.297397893898333</v>
+        <v>8.24923767268108</v>
       </c>
       <c r="E99">
-        <v>16.393</v>
+        <v>16.562</v>
       </c>
       <c r="F99">
-        <v>16.393</v>
+        <v>16.562</v>
       </c>
       <c r="G99">
         <v>0.899</v>
@@ -9393,37 +9393,37 @@
         <v>0.9379999999999999</v>
       </c>
       <c r="M99">
-        <v>3.865469399999999</v>
+        <v>3.905319599999999</v>
       </c>
       <c r="N99">
-        <v>-2.9274694</v>
+        <v>-2.9673196</v>
       </c>
       <c r="O99">
-        <v>-0.8489661259999999</v>
+        <v>-0.8605226839999999</v>
       </c>
       <c r="P99">
-        <v>-2.078503274</v>
+        <v>-2.106796916</v>
       </c>
       <c r="Q99">
-        <v>-1.476503274</v>
+        <v>-1.504796916</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>5.287195421188576</v>
+        <v>7.907893131782864</v>
       </c>
       <c r="T99">
-        <v>32.05572192234067</v>
+        <v>48.08358288351101</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.07037178977538924</v>
+        <v>0.06965371028788528</v>
       </c>
       <c r="W99">
-        <v>0.2192063319709632</v>
+        <v>0.2193756551141167</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9431,7 +9431,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2426613440530663</v>
+        <v>0.2401852078892596</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9439,22 +9439,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.3731460046474918</v>
+        <v>0.3750460046474917</v>
       </c>
       <c r="C100">
-        <v>-7.413762327318917</v>
+        <v>-7.630366706284352</v>
       </c>
       <c r="D100">
-        <v>8.24923767268108</v>
+        <v>8.201633293715647</v>
       </c>
       <c r="E100">
-        <v>16.562</v>
+        <v>16.731</v>
       </c>
       <c r="F100">
-        <v>16.562</v>
+        <v>16.731</v>
       </c>
       <c r="G100">
         <v>0.899</v>
@@ -9475,37 +9475,37 @@
         <v>0.9379999999999999</v>
       </c>
       <c r="M100">
-        <v>3.905319599999999</v>
+        <v>3.9451698</v>
       </c>
       <c r="N100">
-        <v>-2.9673196</v>
+        <v>-3.0071698</v>
       </c>
       <c r="O100">
-        <v>-0.8605226839999999</v>
+        <v>-0.8720792419999999</v>
       </c>
       <c r="P100">
-        <v>-2.106796916</v>
+        <v>-2.135090558</v>
       </c>
       <c r="Q100">
-        <v>-1.504796916</v>
+        <v>-1.533090558</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>7.907893131782864</v>
+        <v>15.76998626356573</v>
       </c>
       <c r="T100">
-        <v>48.08358288351101</v>
+        <v>96.16716576702201</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.06965371028788528</v>
+        <v>0.06895013745669451</v>
       </c>
       <c r="W100">
-        <v>0.2193756551141167</v>
+        <v>0.2195415575877114</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9513,91 +9513,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2401852078892596</v>
+        <v>0.237759094678257</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.3750460046474917</v>
-      </c>
-      <c r="C101">
-        <v>-7.630366706284352</v>
-      </c>
-      <c r="D101">
-        <v>8.201633293715647</v>
-      </c>
-      <c r="E101">
-        <v>16.731</v>
-      </c>
-      <c r="F101">
-        <v>16.731</v>
-      </c>
-      <c r="G101">
-        <v>0.899</v>
-      </c>
-      <c r="H101">
-        <v>16.9</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>1.54</v>
-      </c>
-      <c r="K101">
-        <v>0.6020000000000001</v>
-      </c>
-      <c r="L101">
-        <v>0.9379999999999999</v>
-      </c>
-      <c r="M101">
-        <v>3.9451698</v>
-      </c>
-      <c r="N101">
-        <v>-3.0071698</v>
-      </c>
-      <c r="O101">
-        <v>-0.8720792419999999</v>
-      </c>
-      <c r="P101">
-        <v>-2.135090558</v>
-      </c>
-      <c r="Q101">
-        <v>-1.533090558</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>15.76998626356573</v>
-      </c>
-      <c r="T101">
-        <v>96.16716576702201</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.06895013745669451</v>
-      </c>
-      <c r="W101">
-        <v>0.2195415575877114</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.237759094678257</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
